--- a/data_lake/freight/Cass Freight Index.xlsx
+++ b/data_lake/freight/Cass Freight Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCA3E7A-EF23-4BD9-8D84-BF63A794033D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834A6EB2-FDD2-E348-BA96-57E6EF9D92C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{C4FC06AE-635A-2A42-9884-3F0A165EE3F6}"/>
+    <workbookView xWindow="20" yWindow="600" windowWidth="23020" windowHeight="14620" xr2:uid="{C4FC06AE-635A-2A42-9884-3F0A165EE3F6}"/>
   </bookViews>
   <sheets>
     <sheet name="CFIYOY" sheetId="1" r:id="rId1"/>
@@ -7746,19 +7746,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B411A38B-D5CA-7A4B-9EA2-94E83A5F1DDC}">
   <dimension ref="A1:K426"/>
-  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.58203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.9140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.58203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="8.83203125" style="5" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>33239</v>
       </c>
@@ -7823,7 +7823,7 @@
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>33270</v>
       </c>
@@ -7862,7 +7862,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>33298</v>
       </c>
@@ -7886,7 +7886,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="8"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>33329</v>
       </c>
@@ -7910,7 +7910,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="8"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>33359</v>
       </c>
@@ -7934,7 +7934,7 @@
       <c r="J6" s="7"/>
       <c r="K6" s="8"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>33390</v>
       </c>
@@ -7958,7 +7958,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>33420</v>
       </c>
@@ -7982,7 +7982,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>33451</v>
       </c>
@@ -8006,7 +8006,7 @@
       <c r="J9" s="7"/>
       <c r="K9" s="8"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>33482</v>
       </c>
@@ -8030,7 +8030,7 @@
       <c r="J10" s="7"/>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>33512</v>
       </c>
@@ -8054,7 +8054,7 @@
       <c r="J11" s="7"/>
       <c r="K11" s="8"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>33543</v>
       </c>
@@ -8078,7 +8078,7 @@
       <c r="J12" s="7"/>
       <c r="K12" s="8"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>33573</v>
       </c>
@@ -8102,7 +8102,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>33604</v>
       </c>
@@ -8126,7 +8126,7 @@
       <c r="J14" s="7"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>33635</v>
       </c>
@@ -8150,7 +8150,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>33664</v>
       </c>
@@ -8174,7 +8174,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="8"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>33695</v>
       </c>
@@ -8198,7 +8198,7 @@
       <c r="J17" s="7"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>33725</v>
       </c>
@@ -8222,7 +8222,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>33756</v>
       </c>
@@ -8246,7 +8246,7 @@
       <c r="J19" s="7"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>33786</v>
       </c>
@@ -8270,7 +8270,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>33817</v>
       </c>
@@ -8294,7 +8294,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="8"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>33848</v>
       </c>
@@ -8318,7 +8318,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="8"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>33878</v>
       </c>
@@ -8342,7 +8342,7 @@
       <c r="J23" s="7"/>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>33909</v>
       </c>
@@ -8366,7 +8366,7 @@
       <c r="J24" s="7"/>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>33939</v>
       </c>
@@ -8390,7 +8390,7 @@
       <c r="J25" s="7"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>33970</v>
       </c>
@@ -8414,7 +8414,7 @@
       <c r="J26" s="7"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>34001</v>
       </c>
@@ -8438,7 +8438,7 @@
       <c r="J27" s="7"/>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>34029</v>
       </c>
@@ -8462,7 +8462,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="8"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>34060</v>
       </c>
@@ -8486,7 +8486,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="8"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>34090</v>
       </c>
@@ -8510,7 +8510,7 @@
       <c r="J30" s="7"/>
       <c r="K30" s="8"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>34121</v>
       </c>
@@ -8534,7 +8534,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="8"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>34151</v>
       </c>
@@ -8558,7 +8558,7 @@
       <c r="J32" s="7"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>34182</v>
       </c>
@@ -8582,7 +8582,7 @@
       <c r="J33" s="7"/>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>34213</v>
       </c>
@@ -8606,7 +8606,7 @@
       <c r="J34" s="7"/>
       <c r="K34" s="8"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>34243</v>
       </c>
@@ -8630,7 +8630,7 @@
       <c r="J35" s="7"/>
       <c r="K35" s="8"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>34274</v>
       </c>
@@ -8654,7 +8654,7 @@
       <c r="J36" s="7"/>
       <c r="K36" s="8"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>34304</v>
       </c>
@@ -8678,7 +8678,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="8"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>34335</v>
       </c>
@@ -8702,7 +8702,7 @@
       <c r="J38" s="7"/>
       <c r="K38" s="8"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>34366</v>
       </c>
@@ -8726,7 +8726,7 @@
       <c r="J39" s="7"/>
       <c r="K39" s="8"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>34394</v>
       </c>
@@ -8750,7 +8750,7 @@
       <c r="J40" s="7"/>
       <c r="K40" s="8"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>34425</v>
       </c>
@@ -8774,7 +8774,7 @@
       <c r="J41" s="7"/>
       <c r="K41" s="8"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>34455</v>
       </c>
@@ -8798,7 +8798,7 @@
       <c r="J42" s="7"/>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>34486</v>
       </c>
@@ -8822,7 +8822,7 @@
       <c r="J43" s="7"/>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>34516</v>
       </c>
@@ -8846,7 +8846,7 @@
       <c r="J44" s="7"/>
       <c r="K44" s="8"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>34547</v>
       </c>
@@ -8870,7 +8870,7 @@
       <c r="J45" s="7"/>
       <c r="K45" s="8"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>34578</v>
       </c>
@@ -8894,7 +8894,7 @@
       <c r="J46" s="7"/>
       <c r="K46" s="8"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>34608</v>
       </c>
@@ -8918,7 +8918,7 @@
       <c r="J47" s="7"/>
       <c r="K47" s="8"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>34639</v>
       </c>
@@ -8942,7 +8942,7 @@
       <c r="J48" s="7"/>
       <c r="K48" s="8"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>34669</v>
       </c>
@@ -8966,7 +8966,7 @@
       <c r="J49" s="7"/>
       <c r="K49" s="8"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>34700</v>
       </c>
@@ -8990,7 +8990,7 @@
       <c r="J50" s="7"/>
       <c r="K50" s="8"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>34731</v>
       </c>
@@ -9014,7 +9014,7 @@
       <c r="J51" s="7"/>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>34759</v>
       </c>
@@ -9038,7 +9038,7 @@
       <c r="J52" s="7"/>
       <c r="K52" s="8"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>34790</v>
       </c>
@@ -9062,7 +9062,7 @@
       <c r="J53" s="7"/>
       <c r="K53" s="8"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>34820</v>
       </c>
@@ -9086,7 +9086,7 @@
       <c r="J54" s="7"/>
       <c r="K54" s="8"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>34851</v>
       </c>
@@ -9110,7 +9110,7 @@
       <c r="J55" s="7"/>
       <c r="K55" s="8"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>34881</v>
       </c>
@@ -9134,7 +9134,7 @@
       <c r="J56" s="7"/>
       <c r="K56" s="8"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>34912</v>
       </c>
@@ -9158,7 +9158,7 @@
       <c r="J57" s="7"/>
       <c r="K57" s="8"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>34943</v>
       </c>
@@ -9182,7 +9182,7 @@
       <c r="J58" s="7"/>
       <c r="K58" s="8"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>34973</v>
       </c>
@@ -9206,7 +9206,7 @@
       <c r="J59" s="7"/>
       <c r="K59" s="8"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>35004</v>
       </c>
@@ -9230,7 +9230,7 @@
       <c r="J60" s="7"/>
       <c r="K60" s="8"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>35034</v>
       </c>
@@ -9254,7 +9254,7 @@
       <c r="J61" s="7"/>
       <c r="K61" s="8"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>35065</v>
       </c>
@@ -9278,7 +9278,7 @@
       <c r="J62" s="7"/>
       <c r="K62" s="8"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>35096</v>
       </c>
@@ -9302,7 +9302,7 @@
       <c r="J63" s="7"/>
       <c r="K63" s="8"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>35125</v>
       </c>
@@ -9326,7 +9326,7 @@
       <c r="J64" s="7"/>
       <c r="K64" s="8"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>35156</v>
       </c>
@@ -9350,7 +9350,7 @@
       <c r="J65" s="7"/>
       <c r="K65" s="8"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>35186</v>
       </c>
@@ -9374,7 +9374,7 @@
       <c r="J66" s="7"/>
       <c r="K66" s="8"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>35217</v>
       </c>
@@ -9413,7 +9413,7 @@
       <c r="J67" s="7"/>
       <c r="K67" s="8"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>35247</v>
       </c>
@@ -9437,7 +9437,7 @@
       <c r="J68" s="7"/>
       <c r="K68" s="8"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>35278</v>
       </c>
@@ -9461,7 +9461,7 @@
       <c r="J69" s="7"/>
       <c r="K69" s="8"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>35309</v>
       </c>
@@ -9485,7 +9485,7 @@
       <c r="J70" s="7"/>
       <c r="K70" s="8"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>35339</v>
       </c>
@@ -9509,7 +9509,7 @@
       <c r="J71" s="7"/>
       <c r="K71" s="8"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>35370</v>
       </c>
@@ -9533,7 +9533,7 @@
       <c r="J72" s="7"/>
       <c r="K72" s="8"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>35400</v>
       </c>
@@ -9557,7 +9557,7 @@
       <c r="J73" s="7"/>
       <c r="K73" s="8"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>35431</v>
       </c>
@@ -9581,7 +9581,7 @@
       <c r="J74" s="7"/>
       <c r="K74" s="8"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>35462</v>
       </c>
@@ -9605,7 +9605,7 @@
       <c r="J75" s="7"/>
       <c r="K75" s="8"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>35490</v>
       </c>
@@ -9629,7 +9629,7 @@
       <c r="J76" s="7"/>
       <c r="K76" s="8"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>35521</v>
       </c>
@@ -9653,7 +9653,7 @@
       <c r="J77" s="7"/>
       <c r="K77" s="8"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>35551</v>
       </c>
@@ -9677,7 +9677,7 @@
       <c r="J78" s="7"/>
       <c r="K78" s="8"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>35582</v>
       </c>
@@ -9701,7 +9701,7 @@
       <c r="J79" s="7"/>
       <c r="K79" s="8"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>35612</v>
       </c>
@@ -9725,7 +9725,7 @@
       <c r="J80" s="7"/>
       <c r="K80" s="8"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>35643</v>
       </c>
@@ -9749,7 +9749,7 @@
       <c r="J81" s="7"/>
       <c r="K81" s="8"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>35674</v>
       </c>
@@ -9773,7 +9773,7 @@
       <c r="J82" s="7"/>
       <c r="K82" s="8"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>35704</v>
       </c>
@@ -9797,7 +9797,7 @@
       <c r="J83" s="7"/>
       <c r="K83" s="8"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>35735</v>
       </c>
@@ -9821,7 +9821,7 @@
       <c r="J84" s="7"/>
       <c r="K84" s="8"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>35765</v>
       </c>
@@ -9845,7 +9845,7 @@
       <c r="J85" s="7"/>
       <c r="K85" s="8"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>35796</v>
       </c>
@@ -9869,7 +9869,7 @@
       <c r="J86" s="7"/>
       <c r="K86" s="8"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>35827</v>
       </c>
@@ -9893,7 +9893,7 @@
       <c r="J87" s="7"/>
       <c r="K87" s="8"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>35855</v>
       </c>
@@ -9917,7 +9917,7 @@
       <c r="J88" s="7"/>
       <c r="K88" s="8"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>35886</v>
       </c>
@@ -9941,7 +9941,7 @@
       <c r="J89" s="7"/>
       <c r="K89" s="8"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>35916</v>
       </c>
@@ -9965,7 +9965,7 @@
       <c r="J90" s="7"/>
       <c r="K90" s="8"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>35947</v>
       </c>
@@ -9989,7 +9989,7 @@
       <c r="J91" s="7"/>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>35977</v>
       </c>
@@ -10013,7 +10013,7 @@
       <c r="J92" s="7"/>
       <c r="K92" s="8"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>36008</v>
       </c>
@@ -10037,7 +10037,7 @@
       <c r="J93" s="7"/>
       <c r="K93" s="8"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>36039</v>
       </c>
@@ -10061,7 +10061,7 @@
       <c r="J94" s="7"/>
       <c r="K94" s="8"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>36069</v>
       </c>
@@ -10085,7 +10085,7 @@
       <c r="J95" s="7"/>
       <c r="K95" s="8"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>36100</v>
       </c>
@@ -10109,7 +10109,7 @@
       <c r="J96" s="7"/>
       <c r="K96" s="8"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>36130</v>
       </c>
@@ -10133,7 +10133,7 @@
       <c r="J97" s="7"/>
       <c r="K97" s="8"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>36161</v>
       </c>
@@ -10157,7 +10157,7 @@
       <c r="J98" s="7"/>
       <c r="K98" s="8"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>36192</v>
       </c>
@@ -10181,7 +10181,7 @@
       <c r="J99" s="7"/>
       <c r="K99" s="8"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>36220</v>
       </c>
@@ -10205,7 +10205,7 @@
       <c r="J100" s="7"/>
       <c r="K100" s="8"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>36251</v>
       </c>
@@ -10229,7 +10229,7 @@
       <c r="J101" s="7"/>
       <c r="K101" s="8"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>36281</v>
       </c>
@@ -10253,7 +10253,7 @@
       <c r="J102" s="7"/>
       <c r="K102" s="8"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>36312</v>
       </c>
@@ -10277,7 +10277,7 @@
       <c r="J103" s="7"/>
       <c r="K103" s="8"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>36342</v>
       </c>
@@ -10301,7 +10301,7 @@
       <c r="J104" s="7"/>
       <c r="K104" s="8"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>36373</v>
       </c>
@@ -10325,7 +10325,7 @@
       <c r="J105" s="7"/>
       <c r="K105" s="8"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>36404</v>
       </c>
@@ -10349,7 +10349,7 @@
       <c r="J106" s="7"/>
       <c r="K106" s="8"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>36434</v>
       </c>
@@ -10373,7 +10373,7 @@
       <c r="J107" s="7"/>
       <c r="K107" s="8"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>36465</v>
       </c>
@@ -10397,7 +10397,7 @@
       <c r="J108" s="7"/>
       <c r="K108" s="8"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>36495</v>
       </c>
@@ -10421,7 +10421,7 @@
       <c r="J109" s="7"/>
       <c r="K109" s="8"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>36526</v>
       </c>
@@ -10445,7 +10445,7 @@
       <c r="J110" s="7"/>
       <c r="K110" s="8"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>36557</v>
       </c>
@@ -10469,7 +10469,7 @@
       <c r="J111" s="7"/>
       <c r="K111" s="8"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>36586</v>
       </c>
@@ -10493,7 +10493,7 @@
       <c r="J112" s="7"/>
       <c r="K112" s="8"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>36617</v>
       </c>
@@ -10517,7 +10517,7 @@
       <c r="J113" s="7"/>
       <c r="K113" s="8"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>36647</v>
       </c>
@@ -10541,7 +10541,7 @@
       <c r="J114" s="7"/>
       <c r="K114" s="8"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>36678</v>
       </c>
@@ -10565,7 +10565,7 @@
       <c r="J115" s="7"/>
       <c r="K115" s="8"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>36708</v>
       </c>
@@ -10589,7 +10589,7 @@
       <c r="J116" s="7"/>
       <c r="K116" s="8"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>36739</v>
       </c>
@@ -10613,7 +10613,7 @@
       <c r="J117" s="7"/>
       <c r="K117" s="8"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>36770</v>
       </c>
@@ -10637,7 +10637,7 @@
       <c r="J118" s="7"/>
       <c r="K118" s="8"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>36800</v>
       </c>
@@ -10661,7 +10661,7 @@
       <c r="J119" s="7"/>
       <c r="K119" s="8"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>36831</v>
       </c>
@@ -10685,7 +10685,7 @@
       <c r="J120" s="7"/>
       <c r="K120" s="8"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>36861</v>
       </c>
@@ -10709,7 +10709,7 @@
       <c r="J121" s="7"/>
       <c r="K121" s="8"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>36892</v>
       </c>
@@ -10733,7 +10733,7 @@
       <c r="J122" s="7"/>
       <c r="K122" s="8"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>36923</v>
       </c>
@@ -10757,7 +10757,7 @@
       <c r="J123" s="7"/>
       <c r="K123" s="8"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>36951</v>
       </c>
@@ -10781,7 +10781,7 @@
       <c r="J124" s="7"/>
       <c r="K124" s="8"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>36982</v>
       </c>
@@ -10805,7 +10805,7 @@
       <c r="J125" s="7"/>
       <c r="K125" s="8"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>37012</v>
       </c>
@@ -10829,7 +10829,7 @@
       <c r="J126" s="7"/>
       <c r="K126" s="8"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>37043</v>
       </c>
@@ -10853,7 +10853,7 @@
       <c r="J127" s="7"/>
       <c r="K127" s="8"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>37073</v>
       </c>
@@ -10877,7 +10877,7 @@
       <c r="J128" s="7"/>
       <c r="K128" s="8"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>37104</v>
       </c>
@@ -10901,7 +10901,7 @@
       <c r="J129" s="7"/>
       <c r="K129" s="8"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>37135</v>
       </c>
@@ -10925,7 +10925,7 @@
       <c r="J130" s="7"/>
       <c r="K130" s="8"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>37165</v>
       </c>
@@ -10964,7 +10964,7 @@
       <c r="J131" s="7"/>
       <c r="K131" s="8"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>37196</v>
       </c>
@@ -10988,7 +10988,7 @@
       <c r="J132" s="7"/>
       <c r="K132" s="8"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>37226</v>
       </c>
@@ -11012,7 +11012,7 @@
       <c r="J133" s="7"/>
       <c r="K133" s="8"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>37257</v>
       </c>
@@ -11036,7 +11036,7 @@
       <c r="J134" s="7"/>
       <c r="K134" s="8"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>37288</v>
       </c>
@@ -11060,7 +11060,7 @@
       <c r="J135" s="7"/>
       <c r="K135" s="8"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>37316</v>
       </c>
@@ -11084,7 +11084,7 @@
       <c r="J136" s="7"/>
       <c r="K136" s="8"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>37347</v>
       </c>
@@ -11108,7 +11108,7 @@
       <c r="J137" s="7"/>
       <c r="K137" s="8"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>37377</v>
       </c>
@@ -11132,7 +11132,7 @@
       <c r="J138" s="7"/>
       <c r="K138" s="8"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>37408</v>
       </c>
@@ -11156,7 +11156,7 @@
       <c r="J139" s="7"/>
       <c r="K139" s="8"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>37438</v>
       </c>
@@ -11180,7 +11180,7 @@
       <c r="J140" s="7"/>
       <c r="K140" s="8"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>37469</v>
       </c>
@@ -11204,7 +11204,7 @@
       <c r="J141" s="7"/>
       <c r="K141" s="8"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>37500</v>
       </c>
@@ -11228,7 +11228,7 @@
       <c r="J142" s="7"/>
       <c r="K142" s="8"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>37530</v>
       </c>
@@ -11252,7 +11252,7 @@
       <c r="J143" s="7"/>
       <c r="K143" s="8"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>37561</v>
       </c>
@@ -11276,7 +11276,7 @@
       <c r="J144" s="7"/>
       <c r="K144" s="8"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>37591</v>
       </c>
@@ -11300,7 +11300,7 @@
       <c r="J145" s="7"/>
       <c r="K145" s="8"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>37622</v>
       </c>
@@ -11324,7 +11324,7 @@
       <c r="J146" s="7"/>
       <c r="K146" s="8"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>37653</v>
       </c>
@@ -11348,7 +11348,7 @@
       <c r="J147" s="7"/>
       <c r="K147" s="8"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>37681</v>
       </c>
@@ -11372,7 +11372,7 @@
       <c r="J148" s="7"/>
       <c r="K148" s="8"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>37712</v>
       </c>
@@ -11396,7 +11396,7 @@
       <c r="J149" s="7"/>
       <c r="K149" s="8"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>37742</v>
       </c>
@@ -11420,7 +11420,7 @@
       <c r="J150" s="7"/>
       <c r="K150" s="8"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>37773</v>
       </c>
@@ -11444,7 +11444,7 @@
       <c r="J151" s="7"/>
       <c r="K151" s="8"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>37803</v>
       </c>
@@ -11468,7 +11468,7 @@
       <c r="J152" s="7"/>
       <c r="K152" s="8"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>37834</v>
       </c>
@@ -11492,7 +11492,7 @@
       <c r="J153" s="7"/>
       <c r="K153" s="8"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>37865</v>
       </c>
@@ -11516,7 +11516,7 @@
       <c r="J154" s="7"/>
       <c r="K154" s="8"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>37895</v>
       </c>
@@ -11540,7 +11540,7 @@
       <c r="J155" s="7"/>
       <c r="K155" s="8"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>37926</v>
       </c>
@@ -11564,7 +11564,7 @@
       <c r="J156" s="7"/>
       <c r="K156" s="8"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>37956</v>
       </c>
@@ -11588,7 +11588,7 @@
       <c r="J157" s="7"/>
       <c r="K157" s="8"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>37987</v>
       </c>
@@ -11612,7 +11612,7 @@
       <c r="J158" s="7"/>
       <c r="K158" s="8"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>38018</v>
       </c>
@@ -11636,7 +11636,7 @@
       <c r="J159" s="7"/>
       <c r="K159" s="8"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>38047</v>
       </c>
@@ -11660,7 +11660,7 @@
       <c r="J160" s="7"/>
       <c r="K160" s="8"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>38078</v>
       </c>
@@ -11684,7 +11684,7 @@
       <c r="J161" s="7"/>
       <c r="K161" s="8"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>38108</v>
       </c>
@@ -11708,7 +11708,7 @@
       <c r="J162" s="7"/>
       <c r="K162" s="8"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>38139</v>
       </c>
@@ -11732,7 +11732,7 @@
       <c r="J163" s="7"/>
       <c r="K163" s="8"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>38169</v>
       </c>
@@ -11756,7 +11756,7 @@
       <c r="J164" s="7"/>
       <c r="K164" s="8"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>38200</v>
       </c>
@@ -11780,7 +11780,7 @@
       <c r="J165" s="7"/>
       <c r="K165" s="8"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>38231</v>
       </c>
@@ -11804,7 +11804,7 @@
       <c r="J166" s="7"/>
       <c r="K166" s="8"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>38261</v>
       </c>
@@ -11828,7 +11828,7 @@
       <c r="J167" s="7"/>
       <c r="K167" s="8"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>38292</v>
       </c>
@@ -11852,7 +11852,7 @@
       <c r="J168" s="7"/>
       <c r="K168" s="8"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>38322</v>
       </c>
@@ -11876,7 +11876,7 @@
       <c r="J169" s="7"/>
       <c r="K169" s="8"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>38353</v>
       </c>
@@ -11900,7 +11900,7 @@
       <c r="J170" s="7"/>
       <c r="K170" s="8"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>38384</v>
       </c>
@@ -11924,7 +11924,7 @@
       <c r="J171" s="7"/>
       <c r="K171" s="8"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>38412</v>
       </c>
@@ -11948,7 +11948,7 @@
       <c r="J172" s="7"/>
       <c r="K172" s="8"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>38443</v>
       </c>
@@ -11972,7 +11972,7 @@
       <c r="J173" s="7"/>
       <c r="K173" s="8"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>38473</v>
       </c>
@@ -11996,7 +11996,7 @@
       <c r="J174" s="7"/>
       <c r="K174" s="8"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>38504</v>
       </c>
@@ -12020,7 +12020,7 @@
       <c r="J175" s="7"/>
       <c r="K175" s="8"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>38534</v>
       </c>
@@ -12044,7 +12044,7 @@
       <c r="J176" s="7"/>
       <c r="K176" s="8"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>38565</v>
       </c>
@@ -12068,7 +12068,7 @@
       <c r="J177" s="7"/>
       <c r="K177" s="8"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>38596</v>
       </c>
@@ -12092,7 +12092,7 @@
       <c r="J178" s="7"/>
       <c r="K178" s="8"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>38626</v>
       </c>
@@ -12116,7 +12116,7 @@
       <c r="J179" s="7"/>
       <c r="K179" s="8"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>38657</v>
       </c>
@@ -12140,7 +12140,7 @@
       <c r="J180" s="7"/>
       <c r="K180" s="8"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>38687</v>
       </c>
@@ -12164,7 +12164,7 @@
       <c r="J181" s="7"/>
       <c r="K181" s="8"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>38718</v>
       </c>
@@ -12191,7 +12191,7 @@
       <c r="J182" s="7"/>
       <c r="K182" s="8"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>38749</v>
       </c>
@@ -12218,7 +12218,7 @@
       <c r="J183" s="7"/>
       <c r="K183" s="8"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>38777</v>
       </c>
@@ -12245,7 +12245,7 @@
       <c r="J184" s="7"/>
       <c r="K184" s="8"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>38808</v>
       </c>
@@ -12272,7 +12272,7 @@
       <c r="J185" s="7"/>
       <c r="K185" s="8"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>38838</v>
       </c>
@@ -12299,7 +12299,7 @@
       <c r="J186" s="7"/>
       <c r="K186" s="8"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>38869</v>
       </c>
@@ -12326,7 +12326,7 @@
       <c r="J187" s="7"/>
       <c r="K187" s="8"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>38899</v>
       </c>
@@ -12344,7 +12344,7 @@
       <c r="J188" s="7"/>
       <c r="K188" s="8"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>38930</v>
       </c>
@@ -12362,7 +12362,7 @@
       <c r="J189" s="7"/>
       <c r="K189" s="8"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>38961</v>
       </c>
@@ -12380,7 +12380,7 @@
       <c r="J190" s="7"/>
       <c r="K190" s="8"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>38991</v>
       </c>
@@ -12398,7 +12398,7 @@
       <c r="J191" s="7"/>
       <c r="K191" s="8"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>39022</v>
       </c>
@@ -12416,7 +12416,7 @@
       <c r="J192" s="7"/>
       <c r="K192" s="8"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>39052</v>
       </c>
@@ -12434,7 +12434,7 @@
       <c r="J193" s="7"/>
       <c r="K193" s="8"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>39083</v>
       </c>
@@ -12452,7 +12452,7 @@
       <c r="J194" s="7"/>
       <c r="K194" s="8"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>39114</v>
       </c>
@@ -12485,7 +12485,7 @@
       <c r="J195" s="7"/>
       <c r="K195" s="8"/>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>39142</v>
       </c>
@@ -12503,7 +12503,7 @@
       <c r="J196" s="7"/>
       <c r="K196" s="8"/>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>39173</v>
       </c>
@@ -12521,7 +12521,7 @@
       <c r="J197" s="7"/>
       <c r="K197" s="8"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>39203</v>
       </c>
@@ -12539,7 +12539,7 @@
       <c r="J198" s="7"/>
       <c r="K198" s="8"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>39234</v>
       </c>
@@ -12557,7 +12557,7 @@
       <c r="J199" s="7"/>
       <c r="K199" s="8"/>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>39264</v>
       </c>
@@ -12575,7 +12575,7 @@
       <c r="J200" s="7"/>
       <c r="K200" s="8"/>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>39295</v>
       </c>
@@ -12593,7 +12593,7 @@
       <c r="J201" s="7"/>
       <c r="K201" s="8"/>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>39326</v>
       </c>
@@ -12611,7 +12611,7 @@
       <c r="J202" s="7"/>
       <c r="K202" s="8"/>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>39356</v>
       </c>
@@ -12629,7 +12629,7 @@
       <c r="J203" s="7"/>
       <c r="K203" s="8"/>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>39387</v>
       </c>
@@ -12647,7 +12647,7 @@
       <c r="J204" s="7"/>
       <c r="K204" s="8"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>39417</v>
       </c>
@@ -12665,7 +12665,7 @@
       <c r="J205" s="7"/>
       <c r="K205" s="8"/>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>39448</v>
       </c>
@@ -12683,7 +12683,7 @@
       <c r="J206" s="7"/>
       <c r="K206" s="8"/>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>39479</v>
       </c>
@@ -12701,7 +12701,7 @@
       <c r="J207" s="7"/>
       <c r="K207" s="8"/>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>39508</v>
       </c>
@@ -12719,7 +12719,7 @@
       <c r="J208" s="7"/>
       <c r="K208" s="8"/>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>39539</v>
       </c>
@@ -12737,7 +12737,7 @@
       <c r="J209" s="7"/>
       <c r="K209" s="8"/>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>39569</v>
       </c>
@@ -12755,7 +12755,7 @@
       <c r="J210" s="7"/>
       <c r="K210" s="8"/>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>39600</v>
       </c>
@@ -12773,7 +12773,7 @@
       <c r="J211" s="7"/>
       <c r="K211" s="8"/>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>39630</v>
       </c>
@@ -12791,7 +12791,7 @@
       <c r="J212" s="7"/>
       <c r="K212" s="8"/>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>39661</v>
       </c>
@@ -12809,7 +12809,7 @@
       <c r="J213" s="7"/>
       <c r="K213" s="8"/>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>39692</v>
       </c>
@@ -12827,7 +12827,7 @@
       <c r="J214" s="7"/>
       <c r="K214" s="8"/>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>39722</v>
       </c>
@@ -12845,7 +12845,7 @@
       <c r="J215" s="7"/>
       <c r="K215" s="8"/>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>39753</v>
       </c>
@@ -12863,7 +12863,7 @@
       <c r="J216" s="7"/>
       <c r="K216" s="8"/>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>39783</v>
       </c>
@@ -12881,7 +12881,7 @@
       <c r="J217" s="7"/>
       <c r="K217" s="8"/>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>39814</v>
       </c>
@@ -12899,7 +12899,7 @@
       <c r="J218" s="7"/>
       <c r="K218" s="8"/>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>39845</v>
       </c>
@@ -12917,7 +12917,7 @@
       <c r="J219" s="7"/>
       <c r="K219" s="8"/>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>39873</v>
       </c>
@@ -12935,7 +12935,7 @@
       <c r="J220" s="7"/>
       <c r="K220" s="8"/>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>39904</v>
       </c>
@@ -12953,7 +12953,7 @@
       <c r="J221" s="7"/>
       <c r="K221" s="8"/>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>39934</v>
       </c>
@@ -12971,7 +12971,7 @@
       <c r="J222" s="7"/>
       <c r="K222" s="8"/>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>39965</v>
       </c>
@@ -12989,7 +12989,7 @@
       <c r="J223" s="7"/>
       <c r="K223" s="8"/>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>39995</v>
       </c>
@@ -13007,7 +13007,7 @@
       <c r="J224" s="7"/>
       <c r="K224" s="8"/>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>40026</v>
       </c>
@@ -13025,7 +13025,7 @@
       <c r="J225" s="7"/>
       <c r="K225" s="8"/>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>40057</v>
       </c>
@@ -13043,7 +13043,7 @@
       <c r="J226" s="7"/>
       <c r="K226" s="8"/>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>40087</v>
       </c>
@@ -13061,7 +13061,7 @@
       <c r="J227" s="7"/>
       <c r="K227" s="8"/>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>40118</v>
       </c>
@@ -13079,7 +13079,7 @@
       <c r="J228" s="7"/>
       <c r="K228" s="8"/>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>40148</v>
       </c>
@@ -13097,7 +13097,7 @@
       <c r="J229" s="7"/>
       <c r="K229" s="8"/>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>40179</v>
       </c>
@@ -13115,7 +13115,7 @@
       <c r="J230" s="7"/>
       <c r="K230" s="8"/>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>40210</v>
       </c>
@@ -13133,7 +13133,7 @@
       <c r="J231" s="7"/>
       <c r="K231" s="8"/>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>40238</v>
       </c>
@@ -13151,7 +13151,7 @@
       <c r="J232" s="7"/>
       <c r="K232" s="8"/>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>40269</v>
       </c>
@@ -13169,7 +13169,7 @@
       <c r="J233" s="7"/>
       <c r="K233" s="8"/>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>40299</v>
       </c>
@@ -13187,7 +13187,7 @@
       <c r="J234" s="7"/>
       <c r="K234" s="8"/>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>40330</v>
       </c>
@@ -13205,7 +13205,7 @@
       <c r="J235" s="7"/>
       <c r="K235" s="8"/>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>40360</v>
       </c>
@@ -13223,7 +13223,7 @@
       <c r="J236" s="7"/>
       <c r="K236" s="8"/>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>40391</v>
       </c>
@@ -13241,7 +13241,7 @@
       <c r="J237" s="7"/>
       <c r="K237" s="8"/>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>40422</v>
       </c>
@@ -13259,7 +13259,7 @@
       <c r="J238" s="7"/>
       <c r="K238" s="8"/>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>40452</v>
       </c>
@@ -13277,7 +13277,7 @@
       <c r="J239" s="7"/>
       <c r="K239" s="8"/>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>40483</v>
       </c>
@@ -13295,7 +13295,7 @@
       <c r="J240" s="7"/>
       <c r="K240" s="8"/>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>40513</v>
       </c>
@@ -13313,7 +13313,7 @@
       <c r="J241" s="7"/>
       <c r="K241" s="8"/>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>40544</v>
       </c>
@@ -13331,7 +13331,7 @@
       <c r="J242" s="7"/>
       <c r="K242" s="8"/>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>40575</v>
       </c>
@@ -13349,7 +13349,7 @@
       <c r="J243" s="7"/>
       <c r="K243" s="8"/>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>40603</v>
       </c>
@@ -13367,7 +13367,7 @@
       <c r="J244" s="7"/>
       <c r="K244" s="8"/>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
         <v>40634</v>
       </c>
@@ -13385,7 +13385,7 @@
       <c r="J245" s="7"/>
       <c r="K245" s="8"/>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
         <v>40664</v>
       </c>
@@ -13403,7 +13403,7 @@
       <c r="J246" s="7"/>
       <c r="K246" s="8"/>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
         <v>40695</v>
       </c>
@@ -13421,7 +13421,7 @@
       <c r="J247" s="7"/>
       <c r="K247" s="8"/>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A248" s="2">
         <v>40725</v>
       </c>
@@ -13439,7 +13439,7 @@
       <c r="J248" s="7"/>
       <c r="K248" s="8"/>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
         <v>40756</v>
       </c>
@@ -13457,7 +13457,7 @@
       <c r="J249" s="7"/>
       <c r="K249" s="8"/>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
         <v>40787</v>
       </c>
@@ -13475,7 +13475,7 @@
       <c r="J250" s="7"/>
       <c r="K250" s="8"/>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A251" s="2">
         <v>40817</v>
       </c>
@@ -13493,7 +13493,7 @@
       <c r="J251" s="7"/>
       <c r="K251" s="8"/>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A252" s="2">
         <v>40848</v>
       </c>
@@ -13511,7 +13511,7 @@
       <c r="J252" s="7"/>
       <c r="K252" s="8"/>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
         <v>40878</v>
       </c>
@@ -13529,7 +13529,7 @@
       <c r="J253" s="7"/>
       <c r="K253" s="8"/>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
         <v>40909</v>
       </c>
@@ -13547,7 +13547,7 @@
       <c r="J254" s="7"/>
       <c r="K254" s="8"/>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
         <v>40940</v>
       </c>
@@ -13565,7 +13565,7 @@
       <c r="J255" s="7"/>
       <c r="K255" s="8"/>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>40969</v>
       </c>
@@ -13583,7 +13583,7 @@
       <c r="J256" s="7"/>
       <c r="K256" s="8"/>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>41000</v>
       </c>
@@ -13601,7 +13601,7 @@
       <c r="J257" s="7"/>
       <c r="K257" s="8"/>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>41030</v>
       </c>
@@ -13619,7 +13619,7 @@
       <c r="J258" s="7"/>
       <c r="K258" s="8"/>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>41061</v>
       </c>
@@ -13652,7 +13652,7 @@
       <c r="J259" s="7"/>
       <c r="K259" s="8"/>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>41091</v>
       </c>
@@ -13670,7 +13670,7 @@
       <c r="J260" s="7"/>
       <c r="K260" s="8"/>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>41122</v>
       </c>
@@ -13688,7 +13688,7 @@
       <c r="J261" s="7"/>
       <c r="K261" s="8"/>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>41153</v>
       </c>
@@ -13706,7 +13706,7 @@
       <c r="J262" s="7"/>
       <c r="K262" s="8"/>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
         <v>41183</v>
       </c>
@@ -13724,7 +13724,7 @@
       <c r="J263" s="7"/>
       <c r="K263" s="8"/>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>41214</v>
       </c>
@@ -13742,7 +13742,7 @@
       <c r="J264" s="7"/>
       <c r="K264" s="8"/>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
         <v>41244</v>
       </c>
@@ -13760,7 +13760,7 @@
       <c r="J265" s="7"/>
       <c r="K265" s="8"/>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A266" s="2">
         <v>41275</v>
       </c>
@@ -13778,7 +13778,7 @@
       <c r="J266" s="7"/>
       <c r="K266" s="8"/>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A267" s="2">
         <v>41306</v>
       </c>
@@ -13796,7 +13796,7 @@
       <c r="J267" s="7"/>
       <c r="K267" s="8"/>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
         <v>41334</v>
       </c>
@@ -13814,7 +13814,7 @@
       <c r="J268" s="7"/>
       <c r="K268" s="8"/>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
         <v>41365</v>
       </c>
@@ -13832,7 +13832,7 @@
       <c r="J269" s="7"/>
       <c r="K269" s="8"/>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
         <v>41395</v>
       </c>
@@ -13850,7 +13850,7 @@
       <c r="J270" s="7"/>
       <c r="K270" s="8"/>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
         <v>41426</v>
       </c>
@@ -13868,7 +13868,7 @@
       <c r="J271" s="7"/>
       <c r="K271" s="8"/>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
         <v>41456</v>
       </c>
@@ -13886,7 +13886,7 @@
       <c r="J272" s="7"/>
       <c r="K272" s="8"/>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
         <v>41487</v>
       </c>
@@ -13904,7 +13904,7 @@
       <c r="J273" s="7"/>
       <c r="K273" s="8"/>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
         <v>41518</v>
       </c>
@@ -13922,7 +13922,7 @@
       <c r="J274" s="7"/>
       <c r="K274" s="8"/>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
         <v>41548</v>
       </c>
@@ -13940,7 +13940,7 @@
       <c r="J275" s="7"/>
       <c r="K275" s="8"/>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
         <v>41579</v>
       </c>
@@ -13958,7 +13958,7 @@
       <c r="J276" s="7"/>
       <c r="K276" s="8"/>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
         <v>41609</v>
       </c>
@@ -13976,7 +13976,7 @@
       <c r="J277" s="7"/>
       <c r="K277" s="8"/>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>41640</v>
       </c>
@@ -13994,7 +13994,7 @@
       <c r="J278" s="7"/>
       <c r="K278" s="8"/>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>41671</v>
       </c>
@@ -14012,7 +14012,7 @@
       <c r="J279" s="7"/>
       <c r="K279" s="8"/>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>41699</v>
       </c>
@@ -14030,7 +14030,7 @@
       <c r="J280" s="7"/>
       <c r="K280" s="8"/>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>41730</v>
       </c>
@@ -14048,7 +14048,7 @@
       <c r="J281" s="7"/>
       <c r="K281" s="8"/>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>41760</v>
       </c>
@@ -14066,7 +14066,7 @@
       <c r="J282" s="7"/>
       <c r="K282" s="8"/>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>41791</v>
       </c>
@@ -14084,7 +14084,7 @@
       <c r="J283" s="7"/>
       <c r="K283" s="8"/>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>41821</v>
       </c>
@@ -14102,7 +14102,7 @@
       <c r="J284" s="7"/>
       <c r="K284" s="8"/>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>41852</v>
       </c>
@@ -14120,7 +14120,7 @@
       <c r="J285" s="7"/>
       <c r="K285" s="8"/>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>41883</v>
       </c>
@@ -14138,7 +14138,7 @@
       <c r="J286" s="7"/>
       <c r="K286" s="8"/>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>41913</v>
       </c>
@@ -14156,7 +14156,7 @@
       <c r="J287" s="7"/>
       <c r="K287" s="8"/>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>41944</v>
       </c>
@@ -14174,7 +14174,7 @@
       <c r="J288" s="7"/>
       <c r="K288" s="8"/>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>41974</v>
       </c>
@@ -14192,7 +14192,7 @@
       <c r="J289" s="7"/>
       <c r="K289" s="8"/>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
         <v>42005</v>
       </c>
@@ -14210,7 +14210,7 @@
       <c r="J290" s="7"/>
       <c r="K290" s="8"/>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
         <v>42036</v>
       </c>
@@ -14228,7 +14228,7 @@
       <c r="J291" s="7"/>
       <c r="K291" s="8"/>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
         <v>42064</v>
       </c>
@@ -14246,7 +14246,7 @@
       <c r="J292" s="7"/>
       <c r="K292" s="8"/>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
         <v>42095</v>
       </c>
@@ -14264,7 +14264,7 @@
       <c r="J293" s="7"/>
       <c r="K293" s="8"/>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
         <v>42125</v>
       </c>
@@ -14282,7 +14282,7 @@
       <c r="J294" s="7"/>
       <c r="K294" s="8"/>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
         <v>42156</v>
       </c>
@@ -14300,7 +14300,7 @@
       <c r="J295" s="7"/>
       <c r="K295" s="8"/>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
         <v>42186</v>
       </c>
@@ -14318,7 +14318,7 @@
       <c r="J296" s="7"/>
       <c r="K296" s="8"/>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
         <v>42217</v>
       </c>
@@ -14336,7 +14336,7 @@
       <c r="J297" s="7"/>
       <c r="K297" s="8"/>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
         <v>42248</v>
       </c>
@@ -14354,7 +14354,7 @@
       <c r="J298" s="7"/>
       <c r="K298" s="8"/>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" s="2">
         <v>42278</v>
       </c>
@@ -14372,7 +14372,7 @@
       <c r="J299" s="7"/>
       <c r="K299" s="8"/>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A300" s="2">
         <v>42309</v>
       </c>
@@ -14390,7 +14390,7 @@
       <c r="J300" s="7"/>
       <c r="K300" s="8"/>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A301" s="2">
         <v>42339</v>
       </c>
@@ -14408,7 +14408,7 @@
       <c r="J301" s="7"/>
       <c r="K301" s="8"/>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302" s="2">
         <v>42370</v>
       </c>
@@ -14426,7 +14426,7 @@
       <c r="J302" s="7"/>
       <c r="K302" s="8"/>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303" s="2">
         <v>42401</v>
       </c>
@@ -14444,7 +14444,7 @@
       <c r="J303" s="7"/>
       <c r="K303" s="8"/>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304" s="2">
         <v>42430</v>
       </c>
@@ -14462,7 +14462,7 @@
       <c r="J304" s="7"/>
       <c r="K304" s="8"/>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A305" s="2">
         <v>42461</v>
       </c>
@@ -14480,7 +14480,7 @@
       <c r="J305" s="7"/>
       <c r="K305" s="8"/>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A306" s="2">
         <v>42491</v>
       </c>
@@ -14498,7 +14498,7 @@
       <c r="J306" s="7"/>
       <c r="K306" s="8"/>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A307" s="2">
         <v>42522</v>
       </c>
@@ -14516,7 +14516,7 @@
       <c r="J307" s="7"/>
       <c r="K307" s="8"/>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A308" s="2">
         <v>42552</v>
       </c>
@@ -14534,7 +14534,7 @@
       <c r="J308" s="7"/>
       <c r="K308" s="8"/>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A309" s="2">
         <v>42583</v>
       </c>
@@ -14552,7 +14552,7 @@
       <c r="J309" s="7"/>
       <c r="K309" s="8"/>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A310" s="2">
         <v>42614</v>
       </c>
@@ -14570,7 +14570,7 @@
       <c r="J310" s="7"/>
       <c r="K310" s="8"/>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A311" s="2">
         <v>42644</v>
       </c>
@@ -14588,7 +14588,7 @@
       <c r="J311" s="7"/>
       <c r="K311" s="8"/>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A312" s="2">
         <v>42675</v>
       </c>
@@ -14606,7 +14606,7 @@
       <c r="J312" s="7"/>
       <c r="K312" s="8"/>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A313" s="2">
         <v>42705</v>
       </c>
@@ -14624,7 +14624,7 @@
       <c r="J313" s="7"/>
       <c r="K313" s="8"/>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A314" s="2">
         <v>42736</v>
       </c>
@@ -14642,7 +14642,7 @@
       <c r="J314" s="7"/>
       <c r="K314" s="8"/>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315" s="2">
         <v>42767</v>
       </c>
@@ -14660,7 +14660,7 @@
       <c r="J315" s="7"/>
       <c r="K315" s="8"/>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316" s="2">
         <v>42795</v>
       </c>
@@ -14678,7 +14678,7 @@
       <c r="J316" s="7"/>
       <c r="K316" s="8"/>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317" s="2">
         <v>42826</v>
       </c>
@@ -14696,7 +14696,7 @@
       <c r="J317" s="7"/>
       <c r="K317" s="8"/>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318" s="2">
         <v>42856</v>
       </c>
@@ -14714,7 +14714,7 @@
       <c r="J318" s="7"/>
       <c r="K318" s="8"/>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A319" s="2">
         <v>42887</v>
       </c>
@@ -14732,7 +14732,7 @@
       <c r="J319" s="7"/>
       <c r="K319" s="8"/>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A320" s="2">
         <v>42917</v>
       </c>
@@ -14750,7 +14750,7 @@
       <c r="J320" s="7"/>
       <c r="K320" s="8"/>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321" s="2">
         <v>42948</v>
       </c>
@@ -14768,7 +14768,7 @@
       <c r="J321" s="7"/>
       <c r="K321" s="8"/>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322" s="2">
         <v>42979</v>
       </c>
@@ -14786,7 +14786,7 @@
       <c r="J322" s="7"/>
       <c r="K322" s="8"/>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323" s="2">
         <v>43009</v>
       </c>
@@ -14819,7 +14819,7 @@
       <c r="J323" s="7"/>
       <c r="K323" s="8"/>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324" s="2">
         <v>43040</v>
       </c>
@@ -14837,7 +14837,7 @@
       <c r="J324" s="7"/>
       <c r="K324" s="8"/>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325" s="2">
         <v>43070</v>
       </c>
@@ -14855,7 +14855,7 @@
       <c r="J325" s="7"/>
       <c r="K325" s="8"/>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326" s="2">
         <v>43101</v>
       </c>
@@ -14873,7 +14873,7 @@
       <c r="J326" s="7"/>
       <c r="K326" s="8"/>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327" s="2">
         <v>43132</v>
       </c>
@@ -14891,7 +14891,7 @@
       <c r="J327" s="7"/>
       <c r="K327" s="8"/>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328" s="2">
         <v>43160</v>
       </c>
@@ -14909,7 +14909,7 @@
       <c r="J328" s="7"/>
       <c r="K328" s="8"/>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329" s="2">
         <v>43191</v>
       </c>
@@ -14927,7 +14927,7 @@
       <c r="J329" s="7"/>
       <c r="K329" s="8"/>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330" s="2">
         <v>43221</v>
       </c>
@@ -14945,7 +14945,7 @@
       <c r="J330" s="7"/>
       <c r="K330" s="8"/>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331" s="2">
         <v>43252</v>
       </c>
@@ -14963,7 +14963,7 @@
       <c r="J331" s="7"/>
       <c r="K331" s="8"/>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332" s="2">
         <v>43282</v>
       </c>
@@ -14981,7 +14981,7 @@
       <c r="J332" s="7"/>
       <c r="K332" s="8"/>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A333" s="2">
         <v>43313</v>
       </c>
@@ -14999,7 +14999,7 @@
       <c r="J333" s="7"/>
       <c r="K333" s="8"/>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A334" s="2">
         <v>43344</v>
       </c>
@@ -15017,7 +15017,7 @@
       <c r="J334" s="7"/>
       <c r="K334" s="8"/>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A335" s="2">
         <v>43374</v>
       </c>
@@ -15035,7 +15035,7 @@
       <c r="J335" s="7"/>
       <c r="K335" s="8"/>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A336" s="2">
         <v>43405</v>
       </c>
@@ -15053,7 +15053,7 @@
       <c r="J336" s="7"/>
       <c r="K336" s="8"/>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A337" s="2">
         <v>43435</v>
       </c>
@@ -15071,7 +15071,7 @@
       <c r="J337" s="7"/>
       <c r="K337" s="8"/>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A338" s="2">
         <v>43466</v>
       </c>
@@ -15089,7 +15089,7 @@
       <c r="J338" s="7"/>
       <c r="K338" s="8"/>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A339" s="2">
         <v>43497</v>
       </c>
@@ -15107,7 +15107,7 @@
       <c r="J339" s="7"/>
       <c r="K339" s="8"/>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A340" s="2">
         <v>43525</v>
       </c>
@@ -15125,7 +15125,7 @@
       <c r="J340" s="7"/>
       <c r="K340" s="8"/>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A341" s="2">
         <v>43556</v>
       </c>
@@ -15143,7 +15143,7 @@
       <c r="J341" s="7"/>
       <c r="K341" s="8"/>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A342" s="2">
         <v>43586</v>
       </c>
@@ -15161,7 +15161,7 @@
       <c r="J342" s="7"/>
       <c r="K342" s="8"/>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A343" s="2">
         <v>43617</v>
       </c>
@@ -15179,7 +15179,7 @@
       <c r="J343" s="7"/>
       <c r="K343" s="8"/>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A344" s="2">
         <v>43647</v>
       </c>
@@ -15197,7 +15197,7 @@
       <c r="J344" s="7"/>
       <c r="K344" s="8"/>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A345" s="2">
         <v>43678</v>
       </c>
@@ -15215,7 +15215,7 @@
       <c r="J345" s="7"/>
       <c r="K345" s="8"/>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A346" s="2">
         <v>43709</v>
       </c>
@@ -15233,7 +15233,7 @@
       <c r="J346" s="7"/>
       <c r="K346" s="8"/>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A347" s="2">
         <v>43739</v>
       </c>
@@ -15251,7 +15251,7 @@
       <c r="J347" s="7"/>
       <c r="K347" s="8"/>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A348" s="2">
         <v>43770</v>
       </c>
@@ -15269,7 +15269,7 @@
       <c r="J348" s="7"/>
       <c r="K348" s="8"/>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A349" s="2">
         <v>43800</v>
       </c>
@@ -15287,7 +15287,7 @@
       <c r="J349" s="7"/>
       <c r="K349" s="8"/>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A350" s="2">
         <v>43831</v>
       </c>
@@ -15305,7 +15305,7 @@
       <c r="J350" s="7"/>
       <c r="K350" s="8"/>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A351" s="2">
         <v>43862</v>
       </c>
@@ -15323,7 +15323,7 @@
       <c r="J351" s="7"/>
       <c r="K351" s="8"/>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A352" s="2">
         <v>43891</v>
       </c>
@@ -15341,7 +15341,7 @@
       <c r="J352" s="7"/>
       <c r="K352" s="8"/>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A353" s="2">
         <v>43922</v>
       </c>
@@ -15359,7 +15359,7 @@
       <c r="J353" s="7"/>
       <c r="K353" s="8"/>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354" s="2">
         <v>43952</v>
       </c>
@@ -15377,7 +15377,7 @@
       <c r="J354" s="7"/>
       <c r="K354" s="8"/>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A355" s="2">
         <v>43983</v>
       </c>
@@ -15395,7 +15395,7 @@
       <c r="J355" s="7"/>
       <c r="K355" s="8"/>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A356" s="2">
         <v>44013</v>
       </c>
@@ -15413,7 +15413,7 @@
       <c r="J356" s="7"/>
       <c r="K356" s="8"/>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A357" s="2">
         <v>44044</v>
       </c>
@@ -15431,7 +15431,7 @@
       <c r="J357" s="7"/>
       <c r="K357" s="8"/>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A358" s="2">
         <v>44075</v>
       </c>
@@ -15449,7 +15449,7 @@
       <c r="J358" s="7"/>
       <c r="K358" s="8"/>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A359" s="2">
         <v>44105</v>
       </c>
@@ -15467,7 +15467,7 @@
       <c r="J359" s="7"/>
       <c r="K359" s="8"/>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A360" s="2">
         <v>44136</v>
       </c>
@@ -15485,7 +15485,7 @@
       <c r="J360" s="7"/>
       <c r="K360" s="8"/>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A361" s="2">
         <v>44166</v>
       </c>
@@ -15503,7 +15503,7 @@
       <c r="J361" s="7"/>
       <c r="K361" s="8"/>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A362" s="2">
         <v>44197</v>
       </c>
@@ -15521,7 +15521,7 @@
       <c r="J362" s="7"/>
       <c r="K362" s="8"/>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A363" s="2">
         <v>44228</v>
       </c>
@@ -15539,7 +15539,7 @@
       <c r="J363" s="7"/>
       <c r="K363" s="8"/>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A364" s="2">
         <v>44256</v>
       </c>
@@ -15557,7 +15557,7 @@
       <c r="J364" s="7"/>
       <c r="K364" s="8"/>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A365" s="2">
         <v>44287</v>
       </c>
@@ -15575,7 +15575,7 @@
       <c r="J365" s="7"/>
       <c r="K365" s="8"/>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A366" s="2">
         <v>44317</v>
       </c>
@@ -15593,7 +15593,7 @@
       <c r="J366" s="7"/>
       <c r="K366" s="8"/>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A367" s="2">
         <v>44348</v>
       </c>
@@ -15611,7 +15611,7 @@
       <c r="J367" s="7"/>
       <c r="K367" s="8"/>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A368" s="2">
         <v>44378</v>
       </c>
@@ -15629,7 +15629,7 @@
       <c r="J368" s="7"/>
       <c r="K368" s="8"/>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A369" s="2">
         <v>44409</v>
       </c>
@@ -15647,7 +15647,7 @@
       <c r="J369" s="7"/>
       <c r="K369" s="8"/>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A370" s="2">
         <v>44440</v>
       </c>
@@ -15665,7 +15665,7 @@
       <c r="J370" s="7"/>
       <c r="K370" s="8"/>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A371" s="2">
         <v>44470</v>
       </c>
@@ -15683,7 +15683,7 @@
       <c r="J371" s="7"/>
       <c r="K371" s="8"/>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A372" s="2">
         <v>44501</v>
       </c>
@@ -15701,7 +15701,7 @@
       <c r="J372" s="7"/>
       <c r="K372" s="8"/>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A373" s="2">
         <v>44531</v>
       </c>
@@ -15719,7 +15719,7 @@
       <c r="J373" s="7"/>
       <c r="K373" s="8"/>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A374" s="2">
         <v>44562</v>
       </c>
@@ -15737,7 +15737,7 @@
       <c r="J374" s="7"/>
       <c r="K374" s="8"/>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A375" s="2">
         <v>44593</v>
       </c>
@@ -15755,7 +15755,7 @@
       <c r="J375" s="7"/>
       <c r="K375" s="8"/>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A376" s="2">
         <v>44621</v>
       </c>
@@ -15773,7 +15773,7 @@
       <c r="J376" s="7"/>
       <c r="K376" s="8"/>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A377" s="2">
         <v>44652</v>
       </c>
@@ -15791,7 +15791,7 @@
       <c r="J377" s="7"/>
       <c r="K377" s="8"/>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A378" s="2">
         <v>44682</v>
       </c>
@@ -15809,7 +15809,7 @@
       <c r="J378" s="7"/>
       <c r="K378" s="8"/>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A379" s="2">
         <v>44713</v>
       </c>
@@ -15827,7 +15827,7 @@
       <c r="J379" s="7"/>
       <c r="K379" s="8"/>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A380" s="2">
         <v>44743</v>
       </c>
@@ -15845,7 +15845,7 @@
       <c r="J380" s="7"/>
       <c r="K380" s="8"/>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A381" s="2">
         <v>44774</v>
       </c>
@@ -15863,7 +15863,7 @@
       <c r="J381" s="7"/>
       <c r="K381" s="8"/>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A382" s="2">
         <v>44805</v>
       </c>
@@ -15881,7 +15881,7 @@
       <c r="J382" s="7"/>
       <c r="K382" s="8"/>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A383" s="2">
         <v>44835</v>
       </c>
@@ -15899,7 +15899,7 @@
       <c r="J383" s="7"/>
       <c r="K383" s="8"/>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A384" s="2">
         <v>44866</v>
       </c>
@@ -15917,7 +15917,7 @@
       <c r="J384" s="7"/>
       <c r="K384" s="8"/>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A385" s="2">
         <v>44896</v>
       </c>
@@ -15935,7 +15935,7 @@
       <c r="J385" s="7"/>
       <c r="K385" s="8"/>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A386" s="2">
         <v>44927</v>
       </c>
@@ -15953,7 +15953,7 @@
       <c r="J386" s="7"/>
       <c r="K386" s="8"/>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A387" s="2">
         <v>44958</v>
       </c>
@@ -15986,7 +15986,7 @@
       <c r="J387" s="7"/>
       <c r="K387" s="8"/>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A388" s="2">
         <v>44986</v>
       </c>
@@ -16004,7 +16004,7 @@
       <c r="J388" s="7"/>
       <c r="K388" s="8"/>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A389" s="2">
         <v>45017</v>
       </c>
@@ -16022,7 +16022,7 @@
       <c r="J389" s="7"/>
       <c r="K389" s="8"/>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A390" s="2">
         <v>45047</v>
       </c>
@@ -16040,7 +16040,7 @@
       <c r="J390" s="7"/>
       <c r="K390" s="8"/>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A391" s="2">
         <v>45078</v>
       </c>
@@ -16058,7 +16058,7 @@
       <c r="J391" s="7"/>
       <c r="K391" s="8"/>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A392" s="2">
         <v>45108</v>
       </c>
@@ -16076,7 +16076,7 @@
       <c r="J392" s="7"/>
       <c r="K392" s="8"/>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A393" s="2">
         <v>45139</v>
       </c>
@@ -16094,7 +16094,7 @@
       <c r="J393" s="7"/>
       <c r="K393" s="8"/>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A394" s="2">
         <v>45170</v>
       </c>
@@ -16112,7 +16112,7 @@
       <c r="J394" s="7"/>
       <c r="K394" s="8"/>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A395" s="2">
         <v>45200</v>
       </c>
@@ -16130,7 +16130,7 @@
       <c r="J395" s="7"/>
       <c r="K395" s="8"/>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A396" s="2">
         <v>45231</v>
       </c>
@@ -16148,7 +16148,7 @@
       <c r="J396" s="7"/>
       <c r="K396" s="8"/>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A397" s="2">
         <v>45261</v>
       </c>
@@ -16166,7 +16166,7 @@
       <c r="J397" s="7"/>
       <c r="K397" s="8"/>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A398" s="2">
         <v>45292</v>
       </c>
@@ -16184,7 +16184,7 @@
       <c r="J398" s="7"/>
       <c r="K398" s="8"/>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A399" s="2">
         <v>45323</v>
       </c>
@@ -16202,7 +16202,7 @@
       <c r="J399" s="7"/>
       <c r="K399" s="8"/>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A400" s="2">
         <v>45352</v>
       </c>
@@ -16220,7 +16220,7 @@
       <c r="J400" s="7"/>
       <c r="K400" s="8"/>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A401" s="2">
         <v>45383</v>
       </c>
@@ -16238,7 +16238,7 @@
       <c r="J401" s="7"/>
       <c r="K401" s="8"/>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A402" s="2">
         <v>45413</v>
       </c>
@@ -16256,7 +16256,7 @@
       <c r="J402" s="7"/>
       <c r="K402" s="8"/>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A403" s="2">
         <v>45444</v>
       </c>
@@ -16274,7 +16274,7 @@
       <c r="J403" s="7"/>
       <c r="K403" s="8"/>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A404" s="2">
         <v>45474</v>
       </c>
@@ -16292,7 +16292,7 @@
       <c r="J404" s="7"/>
       <c r="K404" s="8"/>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A405" s="2">
         <v>45505</v>
       </c>
@@ -16310,7 +16310,7 @@
       <c r="J405" s="7"/>
       <c r="K405" s="8"/>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A406" s="2">
         <v>45536</v>
       </c>
@@ -16328,7 +16328,7 @@
       <c r="J406" s="7"/>
       <c r="K406" s="8"/>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A407" s="2">
         <v>45566</v>
       </c>
@@ -16346,7 +16346,7 @@
       <c r="J407" s="7"/>
       <c r="K407" s="8"/>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A408" s="2">
         <v>45597</v>
       </c>
@@ -16364,7 +16364,7 @@
       <c r="J408" s="7"/>
       <c r="K408" s="8"/>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A409" s="2">
         <v>45627</v>
       </c>
@@ -16382,7 +16382,7 @@
       <c r="J409" s="7"/>
       <c r="K409" s="8"/>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A410" s="2">
         <v>45658</v>
       </c>
@@ -16400,7 +16400,7 @@
       <c r="J410" s="7"/>
       <c r="K410" s="8"/>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A411" s="2">
         <v>45689</v>
       </c>
@@ -16418,7 +16418,7 @@
       <c r="J411" s="7"/>
       <c r="K411" s="8"/>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A412" s="2">
         <v>45717</v>
       </c>
@@ -16436,7 +16436,7 @@
       <c r="J412" s="7"/>
       <c r="K412" s="8"/>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A413" s="2">
         <v>45748</v>
       </c>
@@ -16454,7 +16454,7 @@
       <c r="J413" s="7"/>
       <c r="K413" s="8"/>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A414" s="2">
         <v>45778</v>
       </c>
@@ -16472,7 +16472,7 @@
       <c r="J414" s="7"/>
       <c r="K414" s="8"/>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A415" s="2">
         <v>45809</v>
       </c>
@@ -16490,7 +16490,7 @@
       <c r="J415" s="7"/>
       <c r="K415" s="8"/>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A416" s="2">
         <v>45839</v>
       </c>
@@ -16508,7 +16508,7 @@
       <c r="J416" s="7"/>
       <c r="K416" s="8"/>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A417" s="2">
         <v>45870</v>
       </c>
@@ -16526,7 +16526,7 @@
       <c r="J417" s="7"/>
       <c r="K417" s="8"/>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A418" s="2">
         <v>45901</v>
       </c>
@@ -16544,7 +16544,7 @@
       <c r="J418" s="7"/>
       <c r="K418" s="8"/>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A419" s="2">
         <v>45931</v>
       </c>
@@ -16562,7 +16562,7 @@
       <c r="J419" s="7"/>
       <c r="K419" s="8"/>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A420" s="2">
         <v>45962</v>
       </c>
@@ -16580,7 +16580,7 @@
       <c r="J420" s="7"/>
       <c r="K420" s="8"/>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A421" s="2">
         <v>45992</v>
       </c>
@@ -16598,7 +16598,7 @@
       <c r="J421" s="7"/>
       <c r="K421" s="8"/>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A422" s="2">
         <v>46023</v>
       </c>
@@ -16616,7 +16616,7 @@
       <c r="J422" s="7"/>
       <c r="K422" s="8"/>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A423" s="2">
         <v>46054</v>
       </c>
@@ -16634,7 +16634,7 @@
       <c r="J423" s="7"/>
       <c r="K423" s="8"/>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A424" s="2">
         <v>46082</v>
       </c>
@@ -16652,7 +16652,7 @@
       <c r="J424" s="7"/>
       <c r="K424" s="8"/>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A425" s="2">
         <v>46113</v>
       </c>
@@ -16670,7 +16670,7 @@
       <c r="J425" s="7"/>
       <c r="K425" s="8"/>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A426" s="2">
         <v>46143</v>
       </c>
@@ -16696,7 +16696,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5924A769-F5DF-CD4C-A19C-C0CC3D918D45}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -16706,9 +16706,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A23A6A5-7257-844F-BE87-B18231376901}">
   <dimension ref="B3:C5"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
@@ -16716,13 +16716,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
       <c r="C4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>

--- a/data_lake/freight/Cass Freight Index.xlsx
+++ b/data_lake/freight/Cass Freight Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834A6EB2-FDD2-E348-BA96-57E6EF9D92C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC231606-0A4D-4292-A535-0CF759473DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="600" windowWidth="23020" windowHeight="14620" xr2:uid="{C4FC06AE-635A-2A42-9884-3F0A165EE3F6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C4FC06AE-635A-2A42-9884-3F0A165EE3F6}"/>
   </bookViews>
   <sheets>
     <sheet name="CFIYOY" sheetId="1" r:id="rId1"/>
@@ -84,14 +84,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -100,20 +115,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -136,28 +143,28 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="백분율" xfId="1" builtinId="5"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -175,7 +182,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7746,19 +7753,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B411A38B-D5CA-7A4B-9EA2-94E83A5F1DDC}">
   <dimension ref="A1:K426"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.83203125" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.81640625" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="10.81640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -7784,7 +7791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>33239</v>
       </c>
@@ -7823,7 +7830,7 @@
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>33270</v>
       </c>
@@ -7862,7 +7869,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>33298</v>
       </c>
@@ -7886,7 +7893,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="8"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>33329</v>
       </c>
@@ -7910,7 +7917,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="8"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>33359</v>
       </c>
@@ -7934,7 +7941,7 @@
       <c r="J6" s="7"/>
       <c r="K6" s="8"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>33390</v>
       </c>
@@ -7958,7 +7965,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>33420</v>
       </c>
@@ -7982,7 +7989,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>33451</v>
       </c>
@@ -8006,7 +8013,7 @@
       <c r="J9" s="7"/>
       <c r="K9" s="8"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>33482</v>
       </c>
@@ -8030,7 +8037,7 @@
       <c r="J10" s="7"/>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>33512</v>
       </c>
@@ -8054,7 +8061,7 @@
       <c r="J11" s="7"/>
       <c r="K11" s="8"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>33543</v>
       </c>
@@ -8078,7 +8085,7 @@
       <c r="J12" s="7"/>
       <c r="K12" s="8"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>33573</v>
       </c>
@@ -8102,7 +8109,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>33604</v>
       </c>
@@ -8126,7 +8133,7 @@
       <c r="J14" s="7"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>33635</v>
       </c>
@@ -8150,7 +8157,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>33664</v>
       </c>
@@ -8174,7 +8181,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="8"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>33695</v>
       </c>
@@ -8198,7 +8205,7 @@
       <c r="J17" s="7"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>33725</v>
       </c>
@@ -8222,7 +8229,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>33756</v>
       </c>
@@ -8246,7 +8253,7 @@
       <c r="J19" s="7"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>33786</v>
       </c>
@@ -8270,7 +8277,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>33817</v>
       </c>
@@ -8294,7 +8301,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="8"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>33848</v>
       </c>
@@ -8318,7 +8325,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="8"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>33878</v>
       </c>
@@ -8342,7 +8349,7 @@
       <c r="J23" s="7"/>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>33909</v>
       </c>
@@ -8366,7 +8373,7 @@
       <c r="J24" s="7"/>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>33939</v>
       </c>
@@ -8390,7 +8397,7 @@
       <c r="J25" s="7"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>33970</v>
       </c>
@@ -8414,7 +8421,7 @@
       <c r="J26" s="7"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>34001</v>
       </c>
@@ -8438,7 +8445,7 @@
       <c r="J27" s="7"/>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>34029</v>
       </c>
@@ -8462,7 +8469,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="8"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>34060</v>
       </c>
@@ -8486,7 +8493,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="8"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>34090</v>
       </c>
@@ -8510,7 +8517,7 @@
       <c r="J30" s="7"/>
       <c r="K30" s="8"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>34121</v>
       </c>
@@ -8534,7 +8541,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="8"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>34151</v>
       </c>
@@ -8558,7 +8565,7 @@
       <c r="J32" s="7"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>34182</v>
       </c>
@@ -8582,7 +8589,7 @@
       <c r="J33" s="7"/>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>34213</v>
       </c>
@@ -8606,7 +8613,7 @@
       <c r="J34" s="7"/>
       <c r="K34" s="8"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34243</v>
       </c>
@@ -8630,7 +8637,7 @@
       <c r="J35" s="7"/>
       <c r="K35" s="8"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>34274</v>
       </c>
@@ -8654,7 +8661,7 @@
       <c r="J36" s="7"/>
       <c r="K36" s="8"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>34304</v>
       </c>
@@ -8678,7 +8685,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="8"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>34335</v>
       </c>
@@ -8702,7 +8709,7 @@
       <c r="J38" s="7"/>
       <c r="K38" s="8"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>34366</v>
       </c>
@@ -8726,7 +8733,7 @@
       <c r="J39" s="7"/>
       <c r="K39" s="8"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>34394</v>
       </c>
@@ -8750,7 +8757,7 @@
       <c r="J40" s="7"/>
       <c r="K40" s="8"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>34425</v>
       </c>
@@ -8774,7 +8781,7 @@
       <c r="J41" s="7"/>
       <c r="K41" s="8"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>34455</v>
       </c>
@@ -8798,7 +8805,7 @@
       <c r="J42" s="7"/>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>34486</v>
       </c>
@@ -8822,7 +8829,7 @@
       <c r="J43" s="7"/>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>34516</v>
       </c>
@@ -8846,7 +8853,7 @@
       <c r="J44" s="7"/>
       <c r="K44" s="8"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>34547</v>
       </c>
@@ -8870,7 +8877,7 @@
       <c r="J45" s="7"/>
       <c r="K45" s="8"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>34578</v>
       </c>
@@ -8894,7 +8901,7 @@
       <c r="J46" s="7"/>
       <c r="K46" s="8"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>34608</v>
       </c>
@@ -8918,7 +8925,7 @@
       <c r="J47" s="7"/>
       <c r="K47" s="8"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>34639</v>
       </c>
@@ -8942,7 +8949,7 @@
       <c r="J48" s="7"/>
       <c r="K48" s="8"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>34669</v>
       </c>
@@ -8966,7 +8973,7 @@
       <c r="J49" s="7"/>
       <c r="K49" s="8"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>34700</v>
       </c>
@@ -8990,7 +8997,7 @@
       <c r="J50" s="7"/>
       <c r="K50" s="8"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>34731</v>
       </c>
@@ -9014,7 +9021,7 @@
       <c r="J51" s="7"/>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>34759</v>
       </c>
@@ -9038,7 +9045,7 @@
       <c r="J52" s="7"/>
       <c r="K52" s="8"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>34790</v>
       </c>
@@ -9062,7 +9069,7 @@
       <c r="J53" s="7"/>
       <c r="K53" s="8"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>34820</v>
       </c>
@@ -9086,7 +9093,7 @@
       <c r="J54" s="7"/>
       <c r="K54" s="8"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>34851</v>
       </c>
@@ -9110,7 +9117,7 @@
       <c r="J55" s="7"/>
       <c r="K55" s="8"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>34881</v>
       </c>
@@ -9134,7 +9141,7 @@
       <c r="J56" s="7"/>
       <c r="K56" s="8"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>34912</v>
       </c>
@@ -9158,7 +9165,7 @@
       <c r="J57" s="7"/>
       <c r="K57" s="8"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>34943</v>
       </c>
@@ -9182,7 +9189,7 @@
       <c r="J58" s="7"/>
       <c r="K58" s="8"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>34973</v>
       </c>
@@ -9206,7 +9213,7 @@
       <c r="J59" s="7"/>
       <c r="K59" s="8"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>35004</v>
       </c>
@@ -9230,7 +9237,7 @@
       <c r="J60" s="7"/>
       <c r="K60" s="8"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>35034</v>
       </c>
@@ -9254,7 +9261,7 @@
       <c r="J61" s="7"/>
       <c r="K61" s="8"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>35065</v>
       </c>
@@ -9278,7 +9285,7 @@
       <c r="J62" s="7"/>
       <c r="K62" s="8"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>35096</v>
       </c>
@@ -9302,7 +9309,7 @@
       <c r="J63" s="7"/>
       <c r="K63" s="8"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>35125</v>
       </c>
@@ -9326,7 +9333,7 @@
       <c r="J64" s="7"/>
       <c r="K64" s="8"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>35156</v>
       </c>
@@ -9350,7 +9357,7 @@
       <c r="J65" s="7"/>
       <c r="K65" s="8"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>35186</v>
       </c>
@@ -9374,7 +9381,7 @@
       <c r="J66" s="7"/>
       <c r="K66" s="8"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>35217</v>
       </c>
@@ -9413,7 +9420,7 @@
       <c r="J67" s="7"/>
       <c r="K67" s="8"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>35247</v>
       </c>
@@ -9437,7 +9444,7 @@
       <c r="J68" s="7"/>
       <c r="K68" s="8"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>35278</v>
       </c>
@@ -9461,7 +9468,7 @@
       <c r="J69" s="7"/>
       <c r="K69" s="8"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>35309</v>
       </c>
@@ -9485,7 +9492,7 @@
       <c r="J70" s="7"/>
       <c r="K70" s="8"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>35339</v>
       </c>
@@ -9509,7 +9516,7 @@
       <c r="J71" s="7"/>
       <c r="K71" s="8"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>35370</v>
       </c>
@@ -9533,7 +9540,7 @@
       <c r="J72" s="7"/>
       <c r="K72" s="8"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>35400</v>
       </c>
@@ -9557,7 +9564,7 @@
       <c r="J73" s="7"/>
       <c r="K73" s="8"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>35431</v>
       </c>
@@ -9581,7 +9588,7 @@
       <c r="J74" s="7"/>
       <c r="K74" s="8"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>35462</v>
       </c>
@@ -9605,7 +9612,7 @@
       <c r="J75" s="7"/>
       <c r="K75" s="8"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>35490</v>
       </c>
@@ -9629,7 +9636,7 @@
       <c r="J76" s="7"/>
       <c r="K76" s="8"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>35521</v>
       </c>
@@ -9653,7 +9660,7 @@
       <c r="J77" s="7"/>
       <c r="K77" s="8"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>35551</v>
       </c>
@@ -9677,7 +9684,7 @@
       <c r="J78" s="7"/>
       <c r="K78" s="8"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>35582</v>
       </c>
@@ -9701,7 +9708,7 @@
       <c r="J79" s="7"/>
       <c r="K79" s="8"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>35612</v>
       </c>
@@ -9725,7 +9732,7 @@
       <c r="J80" s="7"/>
       <c r="K80" s="8"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>35643</v>
       </c>
@@ -9749,7 +9756,7 @@
       <c r="J81" s="7"/>
       <c r="K81" s="8"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>35674</v>
       </c>
@@ -9773,7 +9780,7 @@
       <c r="J82" s="7"/>
       <c r="K82" s="8"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>35704</v>
       </c>
@@ -9797,7 +9804,7 @@
       <c r="J83" s="7"/>
       <c r="K83" s="8"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>35735</v>
       </c>
@@ -9821,7 +9828,7 @@
       <c r="J84" s="7"/>
       <c r="K84" s="8"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>35765</v>
       </c>
@@ -9845,7 +9852,7 @@
       <c r="J85" s="7"/>
       <c r="K85" s="8"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>35796</v>
       </c>
@@ -9869,7 +9876,7 @@
       <c r="J86" s="7"/>
       <c r="K86" s="8"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>35827</v>
       </c>
@@ -9893,7 +9900,7 @@
       <c r="J87" s="7"/>
       <c r="K87" s="8"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>35855</v>
       </c>
@@ -9917,7 +9924,7 @@
       <c r="J88" s="7"/>
       <c r="K88" s="8"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>35886</v>
       </c>
@@ -9941,7 +9948,7 @@
       <c r="J89" s="7"/>
       <c r="K89" s="8"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>35916</v>
       </c>
@@ -9965,7 +9972,7 @@
       <c r="J90" s="7"/>
       <c r="K90" s="8"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>35947</v>
       </c>
@@ -9989,7 +9996,7 @@
       <c r="J91" s="7"/>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>35977</v>
       </c>
@@ -10013,7 +10020,7 @@
       <c r="J92" s="7"/>
       <c r="K92" s="8"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>36008</v>
       </c>
@@ -10037,7 +10044,7 @@
       <c r="J93" s="7"/>
       <c r="K93" s="8"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>36039</v>
       </c>
@@ -10061,7 +10068,7 @@
       <c r="J94" s="7"/>
       <c r="K94" s="8"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>36069</v>
       </c>
@@ -10085,7 +10092,7 @@
       <c r="J95" s="7"/>
       <c r="K95" s="8"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>36100</v>
       </c>
@@ -10109,7 +10116,7 @@
       <c r="J96" s="7"/>
       <c r="K96" s="8"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>36130</v>
       </c>
@@ -10133,7 +10140,7 @@
       <c r="J97" s="7"/>
       <c r="K97" s="8"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>36161</v>
       </c>
@@ -10157,7 +10164,7 @@
       <c r="J98" s="7"/>
       <c r="K98" s="8"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>36192</v>
       </c>
@@ -10181,7 +10188,7 @@
       <c r="J99" s="7"/>
       <c r="K99" s="8"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>36220</v>
       </c>
@@ -10205,7 +10212,7 @@
       <c r="J100" s="7"/>
       <c r="K100" s="8"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>36251</v>
       </c>
@@ -10229,7 +10236,7 @@
       <c r="J101" s="7"/>
       <c r="K101" s="8"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>36281</v>
       </c>
@@ -10253,7 +10260,7 @@
       <c r="J102" s="7"/>
       <c r="K102" s="8"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>36312</v>
       </c>
@@ -10277,7 +10284,7 @@
       <c r="J103" s="7"/>
       <c r="K103" s="8"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>36342</v>
       </c>
@@ -10301,7 +10308,7 @@
       <c r="J104" s="7"/>
       <c r="K104" s="8"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>36373</v>
       </c>
@@ -10325,7 +10332,7 @@
       <c r="J105" s="7"/>
       <c r="K105" s="8"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>36404</v>
       </c>
@@ -10349,7 +10356,7 @@
       <c r="J106" s="7"/>
       <c r="K106" s="8"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>36434</v>
       </c>
@@ -10373,7 +10380,7 @@
       <c r="J107" s="7"/>
       <c r="K107" s="8"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>36465</v>
       </c>
@@ -10397,7 +10404,7 @@
       <c r="J108" s="7"/>
       <c r="K108" s="8"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>36495</v>
       </c>
@@ -10421,7 +10428,7 @@
       <c r="J109" s="7"/>
       <c r="K109" s="8"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>36526</v>
       </c>
@@ -10445,7 +10452,7 @@
       <c r="J110" s="7"/>
       <c r="K110" s="8"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>36557</v>
       </c>
@@ -10469,7 +10476,7 @@
       <c r="J111" s="7"/>
       <c r="K111" s="8"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>36586</v>
       </c>
@@ -10493,7 +10500,7 @@
       <c r="J112" s="7"/>
       <c r="K112" s="8"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>36617</v>
       </c>
@@ -10517,7 +10524,7 @@
       <c r="J113" s="7"/>
       <c r="K113" s="8"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>36647</v>
       </c>
@@ -10541,7 +10548,7 @@
       <c r="J114" s="7"/>
       <c r="K114" s="8"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>36678</v>
       </c>
@@ -10565,7 +10572,7 @@
       <c r="J115" s="7"/>
       <c r="K115" s="8"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>36708</v>
       </c>
@@ -10589,7 +10596,7 @@
       <c r="J116" s="7"/>
       <c r="K116" s="8"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>36739</v>
       </c>
@@ -10613,7 +10620,7 @@
       <c r="J117" s="7"/>
       <c r="K117" s="8"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>36770</v>
       </c>
@@ -10637,7 +10644,7 @@
       <c r="J118" s="7"/>
       <c r="K118" s="8"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>36800</v>
       </c>
@@ -10661,7 +10668,7 @@
       <c r="J119" s="7"/>
       <c r="K119" s="8"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>36831</v>
       </c>
@@ -10685,7 +10692,7 @@
       <c r="J120" s="7"/>
       <c r="K120" s="8"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>36861</v>
       </c>
@@ -10709,7 +10716,7 @@
       <c r="J121" s="7"/>
       <c r="K121" s="8"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>36892</v>
       </c>
@@ -10733,7 +10740,7 @@
       <c r="J122" s="7"/>
       <c r="K122" s="8"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>36923</v>
       </c>
@@ -10757,7 +10764,7 @@
       <c r="J123" s="7"/>
       <c r="K123" s="8"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>36951</v>
       </c>
@@ -10781,7 +10788,7 @@
       <c r="J124" s="7"/>
       <c r="K124" s="8"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>36982</v>
       </c>
@@ -10805,7 +10812,7 @@
       <c r="J125" s="7"/>
       <c r="K125" s="8"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>37012</v>
       </c>
@@ -10829,7 +10836,7 @@
       <c r="J126" s="7"/>
       <c r="K126" s="8"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>37043</v>
       </c>
@@ -10853,7 +10860,7 @@
       <c r="J127" s="7"/>
       <c r="K127" s="8"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>37073</v>
       </c>
@@ -10877,7 +10884,7 @@
       <c r="J128" s="7"/>
       <c r="K128" s="8"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>37104</v>
       </c>
@@ -10901,7 +10908,7 @@
       <c r="J129" s="7"/>
       <c r="K129" s="8"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>37135</v>
       </c>
@@ -10925,7 +10932,7 @@
       <c r="J130" s="7"/>
       <c r="K130" s="8"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>37165</v>
       </c>
@@ -10964,7 +10971,7 @@
       <c r="J131" s="7"/>
       <c r="K131" s="8"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>37196</v>
       </c>
@@ -10988,7 +10995,7 @@
       <c r="J132" s="7"/>
       <c r="K132" s="8"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>37226</v>
       </c>
@@ -11012,7 +11019,7 @@
       <c r="J133" s="7"/>
       <c r="K133" s="8"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>37257</v>
       </c>
@@ -11036,7 +11043,7 @@
       <c r="J134" s="7"/>
       <c r="K134" s="8"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>37288</v>
       </c>
@@ -11060,7 +11067,7 @@
       <c r="J135" s="7"/>
       <c r="K135" s="8"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>37316</v>
       </c>
@@ -11084,7 +11091,7 @@
       <c r="J136" s="7"/>
       <c r="K136" s="8"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>37347</v>
       </c>
@@ -11108,7 +11115,7 @@
       <c r="J137" s="7"/>
       <c r="K137" s="8"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>37377</v>
       </c>
@@ -11132,7 +11139,7 @@
       <c r="J138" s="7"/>
       <c r="K138" s="8"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>37408</v>
       </c>
@@ -11156,7 +11163,7 @@
       <c r="J139" s="7"/>
       <c r="K139" s="8"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>37438</v>
       </c>
@@ -11180,7 +11187,7 @@
       <c r="J140" s="7"/>
       <c r="K140" s="8"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>37469</v>
       </c>
@@ -11204,7 +11211,7 @@
       <c r="J141" s="7"/>
       <c r="K141" s="8"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>37500</v>
       </c>
@@ -11228,7 +11235,7 @@
       <c r="J142" s="7"/>
       <c r="K142" s="8"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>37530</v>
       </c>
@@ -11252,7 +11259,7 @@
       <c r="J143" s="7"/>
       <c r="K143" s="8"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>37561</v>
       </c>
@@ -11276,7 +11283,7 @@
       <c r="J144" s="7"/>
       <c r="K144" s="8"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>37591</v>
       </c>
@@ -11300,7 +11307,7 @@
       <c r="J145" s="7"/>
       <c r="K145" s="8"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>37622</v>
       </c>
@@ -11324,7 +11331,7 @@
       <c r="J146" s="7"/>
       <c r="K146" s="8"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>37653</v>
       </c>
@@ -11348,7 +11355,7 @@
       <c r="J147" s="7"/>
       <c r="K147" s="8"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>37681</v>
       </c>
@@ -11372,7 +11379,7 @@
       <c r="J148" s="7"/>
       <c r="K148" s="8"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>37712</v>
       </c>
@@ -11396,7 +11403,7 @@
       <c r="J149" s="7"/>
       <c r="K149" s="8"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>37742</v>
       </c>
@@ -11420,7 +11427,7 @@
       <c r="J150" s="7"/>
       <c r="K150" s="8"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>37773</v>
       </c>
@@ -11444,7 +11451,7 @@
       <c r="J151" s="7"/>
       <c r="K151" s="8"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>37803</v>
       </c>
@@ -11468,7 +11475,7 @@
       <c r="J152" s="7"/>
       <c r="K152" s="8"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>37834</v>
       </c>
@@ -11492,7 +11499,7 @@
       <c r="J153" s="7"/>
       <c r="K153" s="8"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>37865</v>
       </c>
@@ -11516,7 +11523,7 @@
       <c r="J154" s="7"/>
       <c r="K154" s="8"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>37895</v>
       </c>
@@ -11540,7 +11547,7 @@
       <c r="J155" s="7"/>
       <c r="K155" s="8"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>37926</v>
       </c>
@@ -11564,7 +11571,7 @@
       <c r="J156" s="7"/>
       <c r="K156" s="8"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>37956</v>
       </c>
@@ -11588,7 +11595,7 @@
       <c r="J157" s="7"/>
       <c r="K157" s="8"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>37987</v>
       </c>
@@ -11612,7 +11619,7 @@
       <c r="J158" s="7"/>
       <c r="K158" s="8"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>38018</v>
       </c>
@@ -11636,7 +11643,7 @@
       <c r="J159" s="7"/>
       <c r="K159" s="8"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>38047</v>
       </c>
@@ -11660,7 +11667,7 @@
       <c r="J160" s="7"/>
       <c r="K160" s="8"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>38078</v>
       </c>
@@ -11684,7 +11691,7 @@
       <c r="J161" s="7"/>
       <c r="K161" s="8"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>38108</v>
       </c>
@@ -11708,7 +11715,7 @@
       <c r="J162" s="7"/>
       <c r="K162" s="8"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>38139</v>
       </c>
@@ -11732,7 +11739,7 @@
       <c r="J163" s="7"/>
       <c r="K163" s="8"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>38169</v>
       </c>
@@ -11756,7 +11763,7 @@
       <c r="J164" s="7"/>
       <c r="K164" s="8"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>38200</v>
       </c>
@@ -11780,7 +11787,7 @@
       <c r="J165" s="7"/>
       <c r="K165" s="8"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>38231</v>
       </c>
@@ -11804,7 +11811,7 @@
       <c r="J166" s="7"/>
       <c r="K166" s="8"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>38261</v>
       </c>
@@ -11828,7 +11835,7 @@
       <c r="J167" s="7"/>
       <c r="K167" s="8"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>38292</v>
       </c>
@@ -11852,7 +11859,7 @@
       <c r="J168" s="7"/>
       <c r="K168" s="8"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>38322</v>
       </c>
@@ -11876,7 +11883,7 @@
       <c r="J169" s="7"/>
       <c r="K169" s="8"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>38353</v>
       </c>
@@ -11900,7 +11907,7 @@
       <c r="J170" s="7"/>
       <c r="K170" s="8"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>38384</v>
       </c>
@@ -11924,7 +11931,7 @@
       <c r="J171" s="7"/>
       <c r="K171" s="8"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>38412</v>
       </c>
@@ -11948,7 +11955,7 @@
       <c r="J172" s="7"/>
       <c r="K172" s="8"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>38443</v>
       </c>
@@ -11972,7 +11979,7 @@
       <c r="J173" s="7"/>
       <c r="K173" s="8"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>38473</v>
       </c>
@@ -11996,7 +12003,7 @@
       <c r="J174" s="7"/>
       <c r="K174" s="8"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>38504</v>
       </c>
@@ -12020,7 +12027,7 @@
       <c r="J175" s="7"/>
       <c r="K175" s="8"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>38534</v>
       </c>
@@ -12044,7 +12051,7 @@
       <c r="J176" s="7"/>
       <c r="K176" s="8"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>38565</v>
       </c>
@@ -12068,7 +12075,7 @@
       <c r="J177" s="7"/>
       <c r="K177" s="8"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>38596</v>
       </c>
@@ -12092,7 +12099,7 @@
       <c r="J178" s="7"/>
       <c r="K178" s="8"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>38626</v>
       </c>
@@ -12116,7 +12123,7 @@
       <c r="J179" s="7"/>
       <c r="K179" s="8"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>38657</v>
       </c>
@@ -12140,7 +12147,7 @@
       <c r="J180" s="7"/>
       <c r="K180" s="8"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>38687</v>
       </c>
@@ -12164,7 +12171,7 @@
       <c r="J181" s="7"/>
       <c r="K181" s="8"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>38718</v>
       </c>
@@ -12191,7 +12198,7 @@
       <c r="J182" s="7"/>
       <c r="K182" s="8"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>38749</v>
       </c>
@@ -12218,7 +12225,7 @@
       <c r="J183" s="7"/>
       <c r="K183" s="8"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>38777</v>
       </c>
@@ -12245,7 +12252,7 @@
       <c r="J184" s="7"/>
       <c r="K184" s="8"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>38808</v>
       </c>
@@ -12272,7 +12279,7 @@
       <c r="J185" s="7"/>
       <c r="K185" s="8"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>38838</v>
       </c>
@@ -12299,7 +12306,7 @@
       <c r="J186" s="7"/>
       <c r="K186" s="8"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>38869</v>
       </c>
@@ -12326,7 +12333,7 @@
       <c r="J187" s="7"/>
       <c r="K187" s="8"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
         <v>38899</v>
       </c>
@@ -12344,7 +12351,7 @@
       <c r="J188" s="7"/>
       <c r="K188" s="8"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
         <v>38930</v>
       </c>
@@ -12362,7 +12369,7 @@
       <c r="J189" s="7"/>
       <c r="K189" s="8"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>38961</v>
       </c>
@@ -12380,7 +12387,7 @@
       <c r="J190" s="7"/>
       <c r="K190" s="8"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>38991</v>
       </c>
@@ -12398,7 +12405,7 @@
       <c r="J191" s="7"/>
       <c r="K191" s="8"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>39022</v>
       </c>
@@ -12416,7 +12423,7 @@
       <c r="J192" s="7"/>
       <c r="K192" s="8"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
         <v>39052</v>
       </c>
@@ -12434,7 +12441,7 @@
       <c r="J193" s="7"/>
       <c r="K193" s="8"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>39083</v>
       </c>
@@ -12452,7 +12459,7 @@
       <c r="J194" s="7"/>
       <c r="K194" s="8"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>39114</v>
       </c>
@@ -12485,7 +12492,7 @@
       <c r="J195" s="7"/>
       <c r="K195" s="8"/>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>39142</v>
       </c>
@@ -12503,7 +12510,7 @@
       <c r="J196" s="7"/>
       <c r="K196" s="8"/>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>39173</v>
       </c>
@@ -12521,7 +12528,7 @@
       <c r="J197" s="7"/>
       <c r="K197" s="8"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>39203</v>
       </c>
@@ -12539,7 +12546,7 @@
       <c r="J198" s="7"/>
       <c r="K198" s="8"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>39234</v>
       </c>
@@ -12557,7 +12564,7 @@
       <c r="J199" s="7"/>
       <c r="K199" s="8"/>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>39264</v>
       </c>
@@ -12575,7 +12582,7 @@
       <c r="J200" s="7"/>
       <c r="K200" s="8"/>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>39295</v>
       </c>
@@ -12593,7 +12600,7 @@
       <c r="J201" s="7"/>
       <c r="K201" s="8"/>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>39326</v>
       </c>
@@ -12611,7 +12618,7 @@
       <c r="J202" s="7"/>
       <c r="K202" s="8"/>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
         <v>39356</v>
       </c>
@@ -12629,7 +12636,7 @@
       <c r="J203" s="7"/>
       <c r="K203" s="8"/>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
         <v>39387</v>
       </c>
@@ -12647,7 +12654,7 @@
       <c r="J204" s="7"/>
       <c r="K204" s="8"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>39417</v>
       </c>
@@ -12665,7 +12672,7 @@
       <c r="J205" s="7"/>
       <c r="K205" s="8"/>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
         <v>39448</v>
       </c>
@@ -12683,7 +12690,7 @@
       <c r="J206" s="7"/>
       <c r="K206" s="8"/>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>39479</v>
       </c>
@@ -12701,7 +12708,7 @@
       <c r="J207" s="7"/>
       <c r="K207" s="8"/>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>39508</v>
       </c>
@@ -12719,7 +12726,7 @@
       <c r="J208" s="7"/>
       <c r="K208" s="8"/>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>39539</v>
       </c>
@@ -12737,7 +12744,7 @@
       <c r="J209" s="7"/>
       <c r="K209" s="8"/>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>39569</v>
       </c>
@@ -12755,7 +12762,7 @@
       <c r="J210" s="7"/>
       <c r="K210" s="8"/>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>39600</v>
       </c>
@@ -12773,7 +12780,7 @@
       <c r="J211" s="7"/>
       <c r="K211" s="8"/>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
         <v>39630</v>
       </c>
@@ -12791,7 +12798,7 @@
       <c r="J212" s="7"/>
       <c r="K212" s="8"/>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>39661</v>
       </c>
@@ -12809,7 +12816,7 @@
       <c r="J213" s="7"/>
       <c r="K213" s="8"/>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
         <v>39692</v>
       </c>
@@ -12827,7 +12834,7 @@
       <c r="J214" s="7"/>
       <c r="K214" s="8"/>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
         <v>39722</v>
       </c>
@@ -12845,7 +12852,7 @@
       <c r="J215" s="7"/>
       <c r="K215" s="8"/>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>39753</v>
       </c>
@@ -12863,7 +12870,7 @@
       <c r="J216" s="7"/>
       <c r="K216" s="8"/>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
         <v>39783</v>
       </c>
@@ -12881,7 +12888,7 @@
       <c r="J217" s="7"/>
       <c r="K217" s="8"/>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>39814</v>
       </c>
@@ -12899,7 +12906,7 @@
       <c r="J218" s="7"/>
       <c r="K218" s="8"/>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>39845</v>
       </c>
@@ -12917,7 +12924,7 @@
       <c r="J219" s="7"/>
       <c r="K219" s="8"/>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>39873</v>
       </c>
@@ -12935,7 +12942,7 @@
       <c r="J220" s="7"/>
       <c r="K220" s="8"/>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>39904</v>
       </c>
@@ -12953,7 +12960,7 @@
       <c r="J221" s="7"/>
       <c r="K221" s="8"/>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>39934</v>
       </c>
@@ -12971,7 +12978,7 @@
       <c r="J222" s="7"/>
       <c r="K222" s="8"/>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
         <v>39965</v>
       </c>
@@ -12989,7 +12996,7 @@
       <c r="J223" s="7"/>
       <c r="K223" s="8"/>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>39995</v>
       </c>
@@ -13007,7 +13014,7 @@
       <c r="J224" s="7"/>
       <c r="K224" s="8"/>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>40026</v>
       </c>
@@ -13025,7 +13032,7 @@
       <c r="J225" s="7"/>
       <c r="K225" s="8"/>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
         <v>40057</v>
       </c>
@@ -13043,7 +13050,7 @@
       <c r="J226" s="7"/>
       <c r="K226" s="8"/>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
         <v>40087</v>
       </c>
@@ -13061,7 +13068,7 @@
       <c r="J227" s="7"/>
       <c r="K227" s="8"/>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
         <v>40118</v>
       </c>
@@ -13079,7 +13086,7 @@
       <c r="J228" s="7"/>
       <c r="K228" s="8"/>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
         <v>40148</v>
       </c>
@@ -13097,7 +13104,7 @@
       <c r="J229" s="7"/>
       <c r="K229" s="8"/>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
         <v>40179</v>
       </c>
@@ -13115,7 +13122,7 @@
       <c r="J230" s="7"/>
       <c r="K230" s="8"/>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
         <v>40210</v>
       </c>
@@ -13133,7 +13140,7 @@
       <c r="J231" s="7"/>
       <c r="K231" s="8"/>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
         <v>40238</v>
       </c>
@@ -13151,7 +13158,7 @@
       <c r="J232" s="7"/>
       <c r="K232" s="8"/>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>40269</v>
       </c>
@@ -13169,7 +13176,7 @@
       <c r="J233" s="7"/>
       <c r="K233" s="8"/>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>40299</v>
       </c>
@@ -13187,7 +13194,7 @@
       <c r="J234" s="7"/>
       <c r="K234" s="8"/>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>40330</v>
       </c>
@@ -13205,7 +13212,7 @@
       <c r="J235" s="7"/>
       <c r="K235" s="8"/>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>40360</v>
       </c>
@@ -13223,7 +13230,7 @@
       <c r="J236" s="7"/>
       <c r="K236" s="8"/>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>40391</v>
       </c>
@@ -13241,7 +13248,7 @@
       <c r="J237" s="7"/>
       <c r="K237" s="8"/>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>40422</v>
       </c>
@@ -13259,7 +13266,7 @@
       <c r="J238" s="7"/>
       <c r="K238" s="8"/>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>40452</v>
       </c>
@@ -13277,7 +13284,7 @@
       <c r="J239" s="7"/>
       <c r="K239" s="8"/>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
         <v>40483</v>
       </c>
@@ -13295,7 +13302,7 @@
       <c r="J240" s="7"/>
       <c r="K240" s="8"/>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>40513</v>
       </c>
@@ -13313,7 +13320,7 @@
       <c r="J241" s="7"/>
       <c r="K241" s="8"/>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>40544</v>
       </c>
@@ -13331,7 +13338,7 @@
       <c r="J242" s="7"/>
       <c r="K242" s="8"/>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
         <v>40575</v>
       </c>
@@ -13349,7 +13356,7 @@
       <c r="J243" s="7"/>
       <c r="K243" s="8"/>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>40603</v>
       </c>
@@ -13367,7 +13374,7 @@
       <c r="J244" s="7"/>
       <c r="K244" s="8"/>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
         <v>40634</v>
       </c>
@@ -13385,7 +13392,7 @@
       <c r="J245" s="7"/>
       <c r="K245" s="8"/>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
         <v>40664</v>
       </c>
@@ -13403,7 +13410,7 @@
       <c r="J246" s="7"/>
       <c r="K246" s="8"/>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
         <v>40695</v>
       </c>
@@ -13421,7 +13428,7 @@
       <c r="J247" s="7"/>
       <c r="K247" s="8"/>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
         <v>40725</v>
       </c>
@@ -13439,7 +13446,7 @@
       <c r="J248" s="7"/>
       <c r="K248" s="8"/>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
         <v>40756</v>
       </c>
@@ -13457,7 +13464,7 @@
       <c r="J249" s="7"/>
       <c r="K249" s="8"/>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" s="2">
         <v>40787</v>
       </c>
@@ -13475,7 +13482,7 @@
       <c r="J250" s="7"/>
       <c r="K250" s="8"/>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" s="2">
         <v>40817</v>
       </c>
@@ -13493,7 +13500,7 @@
       <c r="J251" s="7"/>
       <c r="K251" s="8"/>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" s="2">
         <v>40848</v>
       </c>
@@ -13511,7 +13518,7 @@
       <c r="J252" s="7"/>
       <c r="K252" s="8"/>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" s="2">
         <v>40878</v>
       </c>
@@ -13529,7 +13536,7 @@
       <c r="J253" s="7"/>
       <c r="K253" s="8"/>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" s="2">
         <v>40909</v>
       </c>
@@ -13547,7 +13554,7 @@
       <c r="J254" s="7"/>
       <c r="K254" s="8"/>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" s="2">
         <v>40940</v>
       </c>
@@ -13565,7 +13572,7 @@
       <c r="J255" s="7"/>
       <c r="K255" s="8"/>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" s="2">
         <v>40969</v>
       </c>
@@ -13583,7 +13590,7 @@
       <c r="J256" s="7"/>
       <c r="K256" s="8"/>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" s="2">
         <v>41000</v>
       </c>
@@ -13601,7 +13608,7 @@
       <c r="J257" s="7"/>
       <c r="K257" s="8"/>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" s="2">
         <v>41030</v>
       </c>
@@ -13619,7 +13626,7 @@
       <c r="J258" s="7"/>
       <c r="K258" s="8"/>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" s="2">
         <v>41061</v>
       </c>
@@ -13652,7 +13659,7 @@
       <c r="J259" s="7"/>
       <c r="K259" s="8"/>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" s="2">
         <v>41091</v>
       </c>
@@ -13670,7 +13677,7 @@
       <c r="J260" s="7"/>
       <c r="K260" s="8"/>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" s="2">
         <v>41122</v>
       </c>
@@ -13688,7 +13695,7 @@
       <c r="J261" s="7"/>
       <c r="K261" s="8"/>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" s="2">
         <v>41153</v>
       </c>
@@ -13706,7 +13713,7 @@
       <c r="J262" s="7"/>
       <c r="K262" s="8"/>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" s="2">
         <v>41183</v>
       </c>
@@ -13724,7 +13731,7 @@
       <c r="J263" s="7"/>
       <c r="K263" s="8"/>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" s="2">
         <v>41214</v>
       </c>
@@ -13742,7 +13749,7 @@
       <c r="J264" s="7"/>
       <c r="K264" s="8"/>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" s="2">
         <v>41244</v>
       </c>
@@ -13760,7 +13767,7 @@
       <c r="J265" s="7"/>
       <c r="K265" s="8"/>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" s="2">
         <v>41275</v>
       </c>
@@ -13778,7 +13785,7 @@
       <c r="J266" s="7"/>
       <c r="K266" s="8"/>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" s="2">
         <v>41306</v>
       </c>
@@ -13796,7 +13803,7 @@
       <c r="J267" s="7"/>
       <c r="K267" s="8"/>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" s="2">
         <v>41334</v>
       </c>
@@ -13814,7 +13821,7 @@
       <c r="J268" s="7"/>
       <c r="K268" s="8"/>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" s="2">
         <v>41365</v>
       </c>
@@ -13832,7 +13839,7 @@
       <c r="J269" s="7"/>
       <c r="K269" s="8"/>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" s="2">
         <v>41395</v>
       </c>
@@ -13850,7 +13857,7 @@
       <c r="J270" s="7"/>
       <c r="K270" s="8"/>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" s="2">
         <v>41426</v>
       </c>
@@ -13868,7 +13875,7 @@
       <c r="J271" s="7"/>
       <c r="K271" s="8"/>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" s="2">
         <v>41456</v>
       </c>
@@ -13886,7 +13893,7 @@
       <c r="J272" s="7"/>
       <c r="K272" s="8"/>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" s="2">
         <v>41487</v>
       </c>
@@ -13904,7 +13911,7 @@
       <c r="J273" s="7"/>
       <c r="K273" s="8"/>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" s="2">
         <v>41518</v>
       </c>
@@ -13922,7 +13929,7 @@
       <c r="J274" s="7"/>
       <c r="K274" s="8"/>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" s="2">
         <v>41548</v>
       </c>
@@ -13940,7 +13947,7 @@
       <c r="J275" s="7"/>
       <c r="K275" s="8"/>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" s="2">
         <v>41579</v>
       </c>
@@ -13958,7 +13965,7 @@
       <c r="J276" s="7"/>
       <c r="K276" s="8"/>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" s="2">
         <v>41609</v>
       </c>
@@ -13976,7 +13983,7 @@
       <c r="J277" s="7"/>
       <c r="K277" s="8"/>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" s="2">
         <v>41640</v>
       </c>
@@ -13994,7 +14001,7 @@
       <c r="J278" s="7"/>
       <c r="K278" s="8"/>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" s="2">
         <v>41671</v>
       </c>
@@ -14012,7 +14019,7 @@
       <c r="J279" s="7"/>
       <c r="K279" s="8"/>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" s="2">
         <v>41699</v>
       </c>
@@ -14030,7 +14037,7 @@
       <c r="J280" s="7"/>
       <c r="K280" s="8"/>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" s="2">
         <v>41730</v>
       </c>
@@ -14048,7 +14055,7 @@
       <c r="J281" s="7"/>
       <c r="K281" s="8"/>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" s="2">
         <v>41760</v>
       </c>
@@ -14066,7 +14073,7 @@
       <c r="J282" s="7"/>
       <c r="K282" s="8"/>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" s="2">
         <v>41791</v>
       </c>
@@ -14084,7 +14091,7 @@
       <c r="J283" s="7"/>
       <c r="K283" s="8"/>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" s="2">
         <v>41821</v>
       </c>
@@ -14102,7 +14109,7 @@
       <c r="J284" s="7"/>
       <c r="K284" s="8"/>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" s="2">
         <v>41852</v>
       </c>
@@ -14120,7 +14127,7 @@
       <c r="J285" s="7"/>
       <c r="K285" s="8"/>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" s="2">
         <v>41883</v>
       </c>
@@ -14138,7 +14145,7 @@
       <c r="J286" s="7"/>
       <c r="K286" s="8"/>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" s="2">
         <v>41913</v>
       </c>
@@ -14156,7 +14163,7 @@
       <c r="J287" s="7"/>
       <c r="K287" s="8"/>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" s="2">
         <v>41944</v>
       </c>
@@ -14174,7 +14181,7 @@
       <c r="J288" s="7"/>
       <c r="K288" s="8"/>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" s="2">
         <v>41974</v>
       </c>
@@ -14192,7 +14199,7 @@
       <c r="J289" s="7"/>
       <c r="K289" s="8"/>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" s="2">
         <v>42005</v>
       </c>
@@ -14210,7 +14217,7 @@
       <c r="J290" s="7"/>
       <c r="K290" s="8"/>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" s="2">
         <v>42036</v>
       </c>
@@ -14228,7 +14235,7 @@
       <c r="J291" s="7"/>
       <c r="K291" s="8"/>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" s="2">
         <v>42064</v>
       </c>
@@ -14246,7 +14253,7 @@
       <c r="J292" s="7"/>
       <c r="K292" s="8"/>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" s="2">
         <v>42095</v>
       </c>
@@ -14264,7 +14271,7 @@
       <c r="J293" s="7"/>
       <c r="K293" s="8"/>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" s="2">
         <v>42125</v>
       </c>
@@ -14282,7 +14289,7 @@
       <c r="J294" s="7"/>
       <c r="K294" s="8"/>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" s="2">
         <v>42156</v>
       </c>
@@ -14300,7 +14307,7 @@
       <c r="J295" s="7"/>
       <c r="K295" s="8"/>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" s="2">
         <v>42186</v>
       </c>
@@ -14318,7 +14325,7 @@
       <c r="J296" s="7"/>
       <c r="K296" s="8"/>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" s="2">
         <v>42217</v>
       </c>
@@ -14336,7 +14343,7 @@
       <c r="J297" s="7"/>
       <c r="K297" s="8"/>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" s="2">
         <v>42248</v>
       </c>
@@ -14354,7 +14361,7 @@
       <c r="J298" s="7"/>
       <c r="K298" s="8"/>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" s="2">
         <v>42278</v>
       </c>
@@ -14372,7 +14379,7 @@
       <c r="J299" s="7"/>
       <c r="K299" s="8"/>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" s="2">
         <v>42309</v>
       </c>
@@ -14390,7 +14397,7 @@
       <c r="J300" s="7"/>
       <c r="K300" s="8"/>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" s="2">
         <v>42339</v>
       </c>
@@ -14408,7 +14415,7 @@
       <c r="J301" s="7"/>
       <c r="K301" s="8"/>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" s="2">
         <v>42370</v>
       </c>
@@ -14426,7 +14433,7 @@
       <c r="J302" s="7"/>
       <c r="K302" s="8"/>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" s="2">
         <v>42401</v>
       </c>
@@ -14444,7 +14451,7 @@
       <c r="J303" s="7"/>
       <c r="K303" s="8"/>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" s="2">
         <v>42430</v>
       </c>
@@ -14462,7 +14469,7 @@
       <c r="J304" s="7"/>
       <c r="K304" s="8"/>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" s="2">
         <v>42461</v>
       </c>
@@ -14480,7 +14487,7 @@
       <c r="J305" s="7"/>
       <c r="K305" s="8"/>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" s="2">
         <v>42491</v>
       </c>
@@ -14498,7 +14505,7 @@
       <c r="J306" s="7"/>
       <c r="K306" s="8"/>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" s="2">
         <v>42522</v>
       </c>
@@ -14516,7 +14523,7 @@
       <c r="J307" s="7"/>
       <c r="K307" s="8"/>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" s="2">
         <v>42552</v>
       </c>
@@ -14534,7 +14541,7 @@
       <c r="J308" s="7"/>
       <c r="K308" s="8"/>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" s="2">
         <v>42583</v>
       </c>
@@ -14552,7 +14559,7 @@
       <c r="J309" s="7"/>
       <c r="K309" s="8"/>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" s="2">
         <v>42614</v>
       </c>
@@ -14570,7 +14577,7 @@
       <c r="J310" s="7"/>
       <c r="K310" s="8"/>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" s="2">
         <v>42644</v>
       </c>
@@ -14588,7 +14595,7 @@
       <c r="J311" s="7"/>
       <c r="K311" s="8"/>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" s="2">
         <v>42675</v>
       </c>
@@ -14606,7 +14613,7 @@
       <c r="J312" s="7"/>
       <c r="K312" s="8"/>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>42705</v>
       </c>
@@ -14624,7 +14631,7 @@
       <c r="J313" s="7"/>
       <c r="K313" s="8"/>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" s="2">
         <v>42736</v>
       </c>
@@ -14642,7 +14649,7 @@
       <c r="J314" s="7"/>
       <c r="K314" s="8"/>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" s="2">
         <v>42767</v>
       </c>
@@ -14660,7 +14667,7 @@
       <c r="J315" s="7"/>
       <c r="K315" s="8"/>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" s="2">
         <v>42795</v>
       </c>
@@ -14678,7 +14685,7 @@
       <c r="J316" s="7"/>
       <c r="K316" s="8"/>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" s="2">
         <v>42826</v>
       </c>
@@ -14696,7 +14703,7 @@
       <c r="J317" s="7"/>
       <c r="K317" s="8"/>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" s="2">
         <v>42856</v>
       </c>
@@ -14714,7 +14721,7 @@
       <c r="J318" s="7"/>
       <c r="K318" s="8"/>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" s="2">
         <v>42887</v>
       </c>
@@ -14732,7 +14739,7 @@
       <c r="J319" s="7"/>
       <c r="K319" s="8"/>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" s="2">
         <v>42917</v>
       </c>
@@ -14750,7 +14757,7 @@
       <c r="J320" s="7"/>
       <c r="K320" s="8"/>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" s="2">
         <v>42948</v>
       </c>
@@ -14768,7 +14775,7 @@
       <c r="J321" s="7"/>
       <c r="K321" s="8"/>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" s="2">
         <v>42979</v>
       </c>
@@ -14786,7 +14793,7 @@
       <c r="J322" s="7"/>
       <c r="K322" s="8"/>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" s="2">
         <v>43009</v>
       </c>
@@ -14819,7 +14826,7 @@
       <c r="J323" s="7"/>
       <c r="K323" s="8"/>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" s="2">
         <v>43040</v>
       </c>
@@ -14837,7 +14844,7 @@
       <c r="J324" s="7"/>
       <c r="K324" s="8"/>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" s="2">
         <v>43070</v>
       </c>
@@ -14855,7 +14862,7 @@
       <c r="J325" s="7"/>
       <c r="K325" s="8"/>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" s="2">
         <v>43101</v>
       </c>
@@ -14873,7 +14880,7 @@
       <c r="J326" s="7"/>
       <c r="K326" s="8"/>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" s="2">
         <v>43132</v>
       </c>
@@ -14891,7 +14898,7 @@
       <c r="J327" s="7"/>
       <c r="K327" s="8"/>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" s="2">
         <v>43160</v>
       </c>
@@ -14909,7 +14916,7 @@
       <c r="J328" s="7"/>
       <c r="K328" s="8"/>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" s="2">
         <v>43191</v>
       </c>
@@ -14927,7 +14934,7 @@
       <c r="J329" s="7"/>
       <c r="K329" s="8"/>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" s="2">
         <v>43221</v>
       </c>
@@ -14945,7 +14952,7 @@
       <c r="J330" s="7"/>
       <c r="K330" s="8"/>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" s="2">
         <v>43252</v>
       </c>
@@ -14963,7 +14970,7 @@
       <c r="J331" s="7"/>
       <c r="K331" s="8"/>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" s="2">
         <v>43282</v>
       </c>
@@ -14981,7 +14988,7 @@
       <c r="J332" s="7"/>
       <c r="K332" s="8"/>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" s="2">
         <v>43313</v>
       </c>
@@ -14999,7 +15006,7 @@
       <c r="J333" s="7"/>
       <c r="K333" s="8"/>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" s="2">
         <v>43344</v>
       </c>
@@ -15017,7 +15024,7 @@
       <c r="J334" s="7"/>
       <c r="K334" s="8"/>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" s="2">
         <v>43374</v>
       </c>
@@ -15035,7 +15042,7 @@
       <c r="J335" s="7"/>
       <c r="K335" s="8"/>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" s="2">
         <v>43405</v>
       </c>
@@ -15053,7 +15060,7 @@
       <c r="J336" s="7"/>
       <c r="K336" s="8"/>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" s="2">
         <v>43435</v>
       </c>
@@ -15071,7 +15078,7 @@
       <c r="J337" s="7"/>
       <c r="K337" s="8"/>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" s="2">
         <v>43466</v>
       </c>
@@ -15089,7 +15096,7 @@
       <c r="J338" s="7"/>
       <c r="K338" s="8"/>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" s="2">
         <v>43497</v>
       </c>
@@ -15107,7 +15114,7 @@
       <c r="J339" s="7"/>
       <c r="K339" s="8"/>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" s="2">
         <v>43525</v>
       </c>
@@ -15125,7 +15132,7 @@
       <c r="J340" s="7"/>
       <c r="K340" s="8"/>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" s="2">
         <v>43556</v>
       </c>
@@ -15143,7 +15150,7 @@
       <c r="J341" s="7"/>
       <c r="K341" s="8"/>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" s="2">
         <v>43586</v>
       </c>
@@ -15161,7 +15168,7 @@
       <c r="J342" s="7"/>
       <c r="K342" s="8"/>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" s="2">
         <v>43617</v>
       </c>
@@ -15179,7 +15186,7 @@
       <c r="J343" s="7"/>
       <c r="K343" s="8"/>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" s="2">
         <v>43647</v>
       </c>
@@ -15197,7 +15204,7 @@
       <c r="J344" s="7"/>
       <c r="K344" s="8"/>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" s="2">
         <v>43678</v>
       </c>
@@ -15215,7 +15222,7 @@
       <c r="J345" s="7"/>
       <c r="K345" s="8"/>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" s="2">
         <v>43709</v>
       </c>
@@ -15233,7 +15240,7 @@
       <c r="J346" s="7"/>
       <c r="K346" s="8"/>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" s="2">
         <v>43739</v>
       </c>
@@ -15251,7 +15258,7 @@
       <c r="J347" s="7"/>
       <c r="K347" s="8"/>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" s="2">
         <v>43770</v>
       </c>
@@ -15269,7 +15276,7 @@
       <c r="J348" s="7"/>
       <c r="K348" s="8"/>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" s="2">
         <v>43800</v>
       </c>
@@ -15287,7 +15294,7 @@
       <c r="J349" s="7"/>
       <c r="K349" s="8"/>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" s="2">
         <v>43831</v>
       </c>
@@ -15305,7 +15312,7 @@
       <c r="J350" s="7"/>
       <c r="K350" s="8"/>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" s="2">
         <v>43862</v>
       </c>
@@ -15323,7 +15330,7 @@
       <c r="J351" s="7"/>
       <c r="K351" s="8"/>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" s="2">
         <v>43891</v>
       </c>
@@ -15341,7 +15348,7 @@
       <c r="J352" s="7"/>
       <c r="K352" s="8"/>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353" s="2">
         <v>43922</v>
       </c>
@@ -15359,7 +15366,7 @@
       <c r="J353" s="7"/>
       <c r="K353" s="8"/>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354" s="2">
         <v>43952</v>
       </c>
@@ -15377,7 +15384,7 @@
       <c r="J354" s="7"/>
       <c r="K354" s="8"/>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" s="2">
         <v>43983</v>
       </c>
@@ -15395,7 +15402,7 @@
       <c r="J355" s="7"/>
       <c r="K355" s="8"/>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" s="2">
         <v>44013</v>
       </c>
@@ -15413,7 +15420,7 @@
       <c r="J356" s="7"/>
       <c r="K356" s="8"/>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357" s="2">
         <v>44044</v>
       </c>
@@ -15431,7 +15438,7 @@
       <c r="J357" s="7"/>
       <c r="K357" s="8"/>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358" s="2">
         <v>44075</v>
       </c>
@@ -15449,7 +15456,7 @@
       <c r="J358" s="7"/>
       <c r="K358" s="8"/>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359" s="2">
         <v>44105</v>
       </c>
@@ -15467,7 +15474,7 @@
       <c r="J359" s="7"/>
       <c r="K359" s="8"/>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360" s="2">
         <v>44136</v>
       </c>
@@ -15485,7 +15492,7 @@
       <c r="J360" s="7"/>
       <c r="K360" s="8"/>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361" s="2">
         <v>44166</v>
       </c>
@@ -15503,7 +15510,7 @@
       <c r="J361" s="7"/>
       <c r="K361" s="8"/>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" s="2">
         <v>44197</v>
       </c>
@@ -15521,7 +15528,7 @@
       <c r="J362" s="7"/>
       <c r="K362" s="8"/>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363" s="2">
         <v>44228</v>
       </c>
@@ -15539,7 +15546,7 @@
       <c r="J363" s="7"/>
       <c r="K363" s="8"/>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364" s="2">
         <v>44256</v>
       </c>
@@ -15557,7 +15564,7 @@
       <c r="J364" s="7"/>
       <c r="K364" s="8"/>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365" s="2">
         <v>44287</v>
       </c>
@@ -15575,7 +15582,7 @@
       <c r="J365" s="7"/>
       <c r="K365" s="8"/>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A366" s="2">
         <v>44317</v>
       </c>
@@ -15593,7 +15600,7 @@
       <c r="J366" s="7"/>
       <c r="K366" s="8"/>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A367" s="2">
         <v>44348</v>
       </c>
@@ -15611,7 +15618,7 @@
       <c r="J367" s="7"/>
       <c r="K367" s="8"/>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A368" s="2">
         <v>44378</v>
       </c>
@@ -15629,7 +15636,7 @@
       <c r="J368" s="7"/>
       <c r="K368" s="8"/>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" s="2">
         <v>44409</v>
       </c>
@@ -15647,7 +15654,7 @@
       <c r="J369" s="7"/>
       <c r="K369" s="8"/>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" s="2">
         <v>44440</v>
       </c>
@@ -15665,7 +15672,7 @@
       <c r="J370" s="7"/>
       <c r="K370" s="8"/>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" s="2">
         <v>44470</v>
       </c>
@@ -15683,7 +15690,7 @@
       <c r="J371" s="7"/>
       <c r="K371" s="8"/>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" s="2">
         <v>44501</v>
       </c>
@@ -15701,7 +15708,7 @@
       <c r="J372" s="7"/>
       <c r="K372" s="8"/>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" s="2">
         <v>44531</v>
       </c>
@@ -15719,7 +15726,7 @@
       <c r="J373" s="7"/>
       <c r="K373" s="8"/>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" s="2">
         <v>44562</v>
       </c>
@@ -15737,7 +15744,7 @@
       <c r="J374" s="7"/>
       <c r="K374" s="8"/>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" s="2">
         <v>44593</v>
       </c>
@@ -15755,7 +15762,7 @@
       <c r="J375" s="7"/>
       <c r="K375" s="8"/>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" s="2">
         <v>44621</v>
       </c>
@@ -15773,7 +15780,7 @@
       <c r="J376" s="7"/>
       <c r="K376" s="8"/>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" s="2">
         <v>44652</v>
       </c>
@@ -15791,7 +15798,7 @@
       <c r="J377" s="7"/>
       <c r="K377" s="8"/>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" s="2">
         <v>44682</v>
       </c>
@@ -15809,7 +15816,7 @@
       <c r="J378" s="7"/>
       <c r="K378" s="8"/>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" s="2">
         <v>44713</v>
       </c>
@@ -15827,7 +15834,7 @@
       <c r="J379" s="7"/>
       <c r="K379" s="8"/>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" s="2">
         <v>44743</v>
       </c>
@@ -15845,7 +15852,7 @@
       <c r="J380" s="7"/>
       <c r="K380" s="8"/>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" s="2">
         <v>44774</v>
       </c>
@@ -15863,7 +15870,7 @@
       <c r="J381" s="7"/>
       <c r="K381" s="8"/>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" s="2">
         <v>44805</v>
       </c>
@@ -15881,7 +15888,7 @@
       <c r="J382" s="7"/>
       <c r="K382" s="8"/>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" s="2">
         <v>44835</v>
       </c>
@@ -15899,7 +15906,7 @@
       <c r="J383" s="7"/>
       <c r="K383" s="8"/>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" s="2">
         <v>44866</v>
       </c>
@@ -15917,7 +15924,7 @@
       <c r="J384" s="7"/>
       <c r="K384" s="8"/>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" s="2">
         <v>44896</v>
       </c>
@@ -15935,7 +15942,7 @@
       <c r="J385" s="7"/>
       <c r="K385" s="8"/>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" s="2">
         <v>44927</v>
       </c>
@@ -15953,7 +15960,7 @@
       <c r="J386" s="7"/>
       <c r="K386" s="8"/>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" s="2">
         <v>44958</v>
       </c>
@@ -15986,7 +15993,7 @@
       <c r="J387" s="7"/>
       <c r="K387" s="8"/>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" s="2">
         <v>44986</v>
       </c>
@@ -16004,7 +16011,7 @@
       <c r="J388" s="7"/>
       <c r="K388" s="8"/>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" s="2">
         <v>45017</v>
       </c>
@@ -16022,7 +16029,7 @@
       <c r="J389" s="7"/>
       <c r="K389" s="8"/>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" s="2">
         <v>45047</v>
       </c>
@@ -16040,7 +16047,7 @@
       <c r="J390" s="7"/>
       <c r="K390" s="8"/>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" s="2">
         <v>45078</v>
       </c>
@@ -16058,7 +16065,7 @@
       <c r="J391" s="7"/>
       <c r="K391" s="8"/>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" s="2">
         <v>45108</v>
       </c>
@@ -16076,7 +16083,7 @@
       <c r="J392" s="7"/>
       <c r="K392" s="8"/>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" s="2">
         <v>45139</v>
       </c>
@@ -16094,7 +16101,7 @@
       <c r="J393" s="7"/>
       <c r="K393" s="8"/>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" s="2">
         <v>45170</v>
       </c>
@@ -16112,7 +16119,7 @@
       <c r="J394" s="7"/>
       <c r="K394" s="8"/>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" s="2">
         <v>45200</v>
       </c>
@@ -16130,7 +16137,7 @@
       <c r="J395" s="7"/>
       <c r="K395" s="8"/>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" s="2">
         <v>45231</v>
       </c>
@@ -16148,7 +16155,7 @@
       <c r="J396" s="7"/>
       <c r="K396" s="8"/>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" s="2">
         <v>45261</v>
       </c>
@@ -16166,7 +16173,7 @@
       <c r="J397" s="7"/>
       <c r="K397" s="8"/>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" s="2">
         <v>45292</v>
       </c>
@@ -16184,7 +16191,7 @@
       <c r="J398" s="7"/>
       <c r="K398" s="8"/>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" s="2">
         <v>45323</v>
       </c>
@@ -16202,7 +16209,7 @@
       <c r="J399" s="7"/>
       <c r="K399" s="8"/>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" s="2">
         <v>45352</v>
       </c>
@@ -16220,7 +16227,7 @@
       <c r="J400" s="7"/>
       <c r="K400" s="8"/>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" s="2">
         <v>45383</v>
       </c>
@@ -16238,7 +16245,7 @@
       <c r="J401" s="7"/>
       <c r="K401" s="8"/>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" s="2">
         <v>45413</v>
       </c>
@@ -16256,7 +16263,7 @@
       <c r="J402" s="7"/>
       <c r="K402" s="8"/>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" s="2">
         <v>45444</v>
       </c>
@@ -16274,7 +16281,7 @@
       <c r="J403" s="7"/>
       <c r="K403" s="8"/>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" s="2">
         <v>45474</v>
       </c>
@@ -16292,7 +16299,7 @@
       <c r="J404" s="7"/>
       <c r="K404" s="8"/>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" s="2">
         <v>45505</v>
       </c>
@@ -16310,7 +16317,7 @@
       <c r="J405" s="7"/>
       <c r="K405" s="8"/>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" s="2">
         <v>45536</v>
       </c>
@@ -16328,7 +16335,7 @@
       <c r="J406" s="7"/>
       <c r="K406" s="8"/>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" s="2">
         <v>45566</v>
       </c>
@@ -16346,7 +16353,7 @@
       <c r="J407" s="7"/>
       <c r="K407" s="8"/>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="2">
         <v>45597</v>
       </c>
@@ -16364,7 +16371,7 @@
       <c r="J408" s="7"/>
       <c r="K408" s="8"/>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" s="2">
         <v>45627</v>
       </c>
@@ -16382,7 +16389,7 @@
       <c r="J409" s="7"/>
       <c r="K409" s="8"/>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="2">
         <v>45658</v>
       </c>
@@ -16400,7 +16407,7 @@
       <c r="J410" s="7"/>
       <c r="K410" s="8"/>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" s="2">
         <v>45689</v>
       </c>
@@ -16418,7 +16425,7 @@
       <c r="J411" s="7"/>
       <c r="K411" s="8"/>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" s="2">
         <v>45717</v>
       </c>
@@ -16436,7 +16443,7 @@
       <c r="J412" s="7"/>
       <c r="K412" s="8"/>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" s="2">
         <v>45748</v>
       </c>
@@ -16454,7 +16461,7 @@
       <c r="J413" s="7"/>
       <c r="K413" s="8"/>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" s="2">
         <v>45778</v>
       </c>
@@ -16472,7 +16479,7 @@
       <c r="J414" s="7"/>
       <c r="K414" s="8"/>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" s="2">
         <v>45809</v>
       </c>
@@ -16490,7 +16497,7 @@
       <c r="J415" s="7"/>
       <c r="K415" s="8"/>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" s="2">
         <v>45839</v>
       </c>
@@ -16508,7 +16515,7 @@
       <c r="J416" s="7"/>
       <c r="K416" s="8"/>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" s="2">
         <v>45870</v>
       </c>
@@ -16526,7 +16533,7 @@
       <c r="J417" s="7"/>
       <c r="K417" s="8"/>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" s="2">
         <v>45901</v>
       </c>
@@ -16544,7 +16551,7 @@
       <c r="J418" s="7"/>
       <c r="K418" s="8"/>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" s="2">
         <v>45931</v>
       </c>
@@ -16562,7 +16569,7 @@
       <c r="J419" s="7"/>
       <c r="K419" s="8"/>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" s="2">
         <v>45962</v>
       </c>
@@ -16580,7 +16587,7 @@
       <c r="J420" s="7"/>
       <c r="K420" s="8"/>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" s="2">
         <v>45992</v>
       </c>
@@ -16598,7 +16605,7 @@
       <c r="J421" s="7"/>
       <c r="K421" s="8"/>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" s="2">
         <v>46023</v>
       </c>
@@ -16616,7 +16623,7 @@
       <c r="J422" s="7"/>
       <c r="K422" s="8"/>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" s="2">
         <v>46054</v>
       </c>
@@ -16634,7 +16641,7 @@
       <c r="J423" s="7"/>
       <c r="K423" s="8"/>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" s="2">
         <v>46082</v>
       </c>
@@ -16652,7 +16659,7 @@
       <c r="J424" s="7"/>
       <c r="K424" s="8"/>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" s="2">
         <v>46113</v>
       </c>
@@ -16670,7 +16677,7 @@
       <c r="J425" s="7"/>
       <c r="K425" s="8"/>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" s="2">
         <v>46143</v>
       </c>
@@ -16689,6 +16696,7 @@
       <c r="K426" s="8"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16696,8 +16704,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5924A769-F5DF-CD4C-A19C-C0CC3D918D45}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -16706,9 +16715,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A23A6A5-7257-844F-BE87-B18231376901}">
   <dimension ref="B3:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
@@ -16716,13 +16725,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B4" s="1"/>
       <c r="C4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -16731,6 +16740,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>